--- a/deliverable/Work Tracker Demo.xlsx
+++ b/deliverable/Work Tracker Demo.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5994CA44-F997-4488-93FB-892BF4C12129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8C046DA-E49E-4C7E-B805-181713F9980E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F43B3E2-DD9D-43CA-8067-DCABF9417DFA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9621E1EE-779C-450F-87AC-5CDFDDD3B01E}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -18,18 +18,19 @@
     <definedName name="CondOverdue">InScope*(T_Status&lt;&gt;"Done")*ISNUMBER(T_Due)*(T_Due&lt;TODAY())</definedName>
     <definedName name="CondUpcoming">InScope*(T_Status&lt;&gt;"Done")*ISNUMBER(T_Due)*(T_Due&gt;=TODAY())</definedName>
     <definedName name="InScope">(T_Task&lt;&gt;"")*OwnerOK*StatusOK*YearOK</definedName>
-    <definedName name="KpiDone">Dashboard!$D$7</definedName>
-    <definedName name="KpiDueThisWeek">Dashboard!$M$7</definedName>
-    <definedName name="KpiInProgress">Dashboard!$H$7</definedName>
-    <definedName name="KpiOverdue">Dashboard!$J$7</definedName>
-    <definedName name="KpiTotal">Dashboard!$B$7</definedName>
+    <definedName name="KpiDone">Dashboard!$N$8</definedName>
+    <definedName name="KpiDueThisWeek">Dashboard!$G$8</definedName>
+    <definedName name="KpiInProgress">Dashboard!$L$8</definedName>
+    <definedName name="KpiOverdue">Dashboard!$D$8</definedName>
+    <definedName name="KpiTotal">Dashboard!$B$8</definedName>
     <definedName name="OwnerList">Lists!$A$4:INDEX(Lists!$A$4:$A$34,COUNTIF(Lists!$A$4:$A$34,"?*"))</definedName>
     <definedName name="OwnerOK">((SelOwner="(All)")+(SelOwner="")+(T_Owner=SelOwner))&gt;0</definedName>
     <definedName name="OwnerRank">IF(T_Owner="",-1,COUNTIF(T_Owner,"&lt;"&amp;T_Owner))</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Dashboard!$A$1:$R$38</definedName>
     <definedName name="RowNo">ROW(T_ID)-MIN(ROW(T_ID))+1</definedName>
-    <definedName name="SelOwner">Dashboard!$C$4</definedName>
-    <definedName name="SelStatus">Dashboard!$E$4</definedName>
-    <definedName name="SelYear">Dashboard!$I$4</definedName>
+    <definedName name="SelOwner">Dashboard!$C$5</definedName>
+    <definedName name="SelStatus">Dashboard!$E$5</definedName>
+    <definedName name="SelYear">Dashboard!$H$5</definedName>
     <definedName name="SortKey">IF(ISNUMBER(T_Due),T_Due,99999)+RowNo/100000</definedName>
     <definedName name="SortKeyView">IF(T_Status="Done",100000,0)+SortKey</definedName>
     <definedName name="StatusList">Lists!$C$4:$C$8</definedName>
@@ -460,16 +461,34 @@
     <t>TOTAL TASKS</t>
   </si>
   <si>
+    <t>OVERDUE</t>
+  </si>
+  <si>
+    <t>DUE THIS WEEK</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
     <t>DONE</t>
   </si>
   <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>OVERDUE</t>
-  </si>
-  <si>
-    <t>DUE THIS WEEK</t>
+    <t>Tasks in view</t>
+  </si>
+  <si>
+    <t>Flag</t>
+  </si>
+  <si>
+    <t>% done</t>
+  </si>
+  <si>
+    <t>Next 5 due dates</t>
+  </si>
+  <si>
+    <t>Not done, soonest first</t>
+  </si>
+  <si>
+    <t>Days left</t>
   </si>
   <si>
     <t>This Week's Focus</t>
@@ -478,24 +497,6 @@
     <t>Not done, due in the next 7 days</t>
   </si>
   <si>
-    <t>% done</t>
-  </si>
-  <si>
-    <t>Next 5 due dates</t>
-  </si>
-  <si>
-    <t>Not done, soonest first</t>
-  </si>
-  <si>
-    <t>Days left</t>
-  </si>
-  <si>
-    <t>Tasks in view</t>
-  </si>
-  <si>
-    <t>Flag</t>
-  </si>
-  <si>
     <t>Progress by owner</t>
   </si>
   <si>
@@ -532,16 +533,16 @@
     <t>Read the dashboard</t>
   </si>
   <si>
-    <t>Pick an Owner, a Status or a Year in the yellow cells at the top. Everything on the page follows. Choose (All) to clear.</t>
+    <t>Pick an Owner, a Status or a Year in the shaded cells at the top. Everything on the page follows. Choose (All) to clear.</t>
   </si>
   <si>
     <t>Overdue = not Done and the Due date is before today. Due this week = not Done and due today or in the next 6 days.</t>
   </si>
   <si>
-    <t>This Week's Focus shows up to 8 tasks, Next due dates 5, Tasks in view 15. A line under each list says how many more are not shown.</t>
-  </si>
-  <si>
-    <t>In the Tasks sheet, an overdue Due date turns red and one due this week turns amber, by themselves, every day.</t>
+    <t>Tasks in view shows up to 15 tasks, Next due dates 5, This Week's Focus 8. A line under each list says how many more are not shown.</t>
+  </si>
+  <si>
+    <t>In the Tasks sheet, an overdue Due date turns red and says OVERDUE; one due this week turns amber and says so. They update by themselves, every day.</t>
   </si>
   <si>
     <t>Good to know</t>
@@ -559,17 +560,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="0.00000"/>
-    <numFmt numFmtId="166" formatCode="mmm\ d"/>
-    <numFmt numFmtId="167" formatCode="[=0]&quot;today&quot;;[=1]&quot;1 day&quot;;0&quot; days&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="mmm\ d"/>
+    <numFmt numFmtId="169" formatCode="[=0]&quot;today&quot;;[=1]&quot;1 day&quot;;0&quot; days&quot;"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF1F2937"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF5B6B7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF5B6B7F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -577,14 +593,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF6B7785"/>
+      <color rgb="FF1F3A5F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -598,16 +607,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF5B6B7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
-      <sz val="11"/>
-      <color rgb="FF6B7785"/>
+      <sz val="9"/>
+      <color rgb="FF5B6B7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5B6B7F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="36"/>
       <color rgb="FF1F3A5F"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -615,72 +639,16 @@
     </font>
     <font>
       <b/>
-      <sz val="30"/>
-      <color rgb="FF1F3A5F"/>
+      <sz val="36"/>
+      <color rgb="FFB42318"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FF1E7B3A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="30"/>
-      <color rgb="FF1E7B3A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF1B5FAE"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="30"/>
-      <color rgb="FF1B5FAE"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFB42323"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="30"/>
-      <color rgb="FFB42323"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF9A6200"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="30"/>
-      <color rgb="FF9A6200"/>
+      <sz val="36"/>
+      <color rgb="FF7A4A00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -693,16 +661,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF1F3A5F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -711,121 +671,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF1F5"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9E0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8EDF4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F4E8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3EEFB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4E4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF1D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9B7"/>
+        <fgColor rgb="FFE2E8F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="5">
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC9A227"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFC9A227"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC9A227"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC9A227"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFC9A227"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC9A227"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC9A227"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFC9A227"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC9A227"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC9A227"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFFFFFFF"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -836,13 +695,13 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFAEB7C2"/>
+        <color rgb="FF1F3A5F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFE0A526"/>
+      <left style="thick">
+        <color rgb="FF1F3A5F"/>
       </left>
       <right/>
       <top/>
@@ -850,103 +709,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFE0A526"/>
+      <left style="thick">
+        <color rgb="FFB42318"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFAEB7C2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFE0A526"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FFE0A526"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFE0A526"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFE0A526"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFE0A526"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFE0A526"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFE0A526"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFE0A526"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFE0A526"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFAEB7C2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFE0A526"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFE0A526"/>
-      </right>
+      <left style="thick">
+        <color rgb="FF7A4A00"/>
+      </left>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color rgb="FFE0A526"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -956,234 +740,177 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="20">
     <dxf>
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FFB42323"/>
+        <color rgb="FFB42318"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF1F2937"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF1F2937"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF1F2937"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7A4A00"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
-        <color rgb="FF1E7B3A"/>
+        <color rgb="FF2E7D32"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FFC25E00"/>
+        <color rgb="FF7A4A00"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
-        <color rgb="FF1E7B3A"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC25E00"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB42323"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB42323"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB42323"/>
+        <color rgb="FF2E7D32"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
-        <color rgb="FF6B4500"/>
+        <color rgb="FF7A4A00"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFE2A8"/>
+          <bgColor rgb="FFFDE7B0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1195,24 +922,18 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFD64545"/>
+          <bgColor rgb="FFB42318"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB42323"/>
+        <color rgb="FF7A4A00"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF6B4500"/>
-      </font>
+      <numFmt numFmtId="166" formatCode="mmm\ d\,\ yyyy&quot;   this week&quot;"/>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFE2A8"/>
+          <bgColor rgb="FFFDE7B0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1222,17 +943,31 @@
         <i val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
+      <numFmt numFmtId="165" formatCode="mmm\ d\,\ yyyy&quot;   OVERDUE&quot;"/>
       <fill>
         <patternFill>
-          <bgColor rgb="FFD64545"/>
+          <bgColor rgb="FFB42318"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <i/>
+        <color rgb="FF5B6B7F"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1243,8 +978,43 @@
     <dxf>
       <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1F3A5F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F2937"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF5F7FA"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FFE2E8F0"/>
+        </bottom>
+        <horizontal style="thin">
+          <color rgb="FFE2E8F0"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="AZG Table" pivot="0" table="0" count="2" xr9:uid="{152807FA-F056-43F9-8DBA-FF331AEB0691}">
+      <tableStyleElement type="wholeTable" dxfId="19"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1257,24 +1027,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{368ACCC5-A9D8-4DA0-B6EC-F680D3A3DB37}" name="Tasks" displayName="Tasks" ref="A1:K43" totalsRowShown="0">
-  <autoFilter ref="A1:K43" xr:uid="{368ACCC5-A9D8-4DA0-B6EC-F680D3A3DB37}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49590DEB-0070-423E-982E-B237A19237B5}" name="Tasks" displayName="Tasks" ref="A1:K43" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="A1:K43" xr:uid="{49590DEB-0070-423E-982E-B237A19237B5}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{561FBF78-D731-42CA-AB5A-C14D43412355}" name="ID" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{7EAA95EE-5C23-4513-9336-2E484F019F7F}" name="Task"/>
-    <tableColumn id="3" xr3:uid="{7AD66D9E-8D1E-45D7-989A-45143370D946}" name="Owner"/>
-    <tableColumn id="4" xr3:uid="{12C72A98-692B-4554-A5AE-C93ABD5294E8}" name="Department"/>
-    <tableColumn id="5" xr3:uid="{6E101C4C-E1CE-43A5-94A6-C12D55EE62B4}" name="Status"/>
-    <tableColumn id="6" xr3:uid="{4A028575-F7F3-4D82-ABC9-F4C607784D8A}" name="Priority"/>
-    <tableColumn id="7" xr3:uid="{6B43A1F1-9FEE-4D56-906A-672EB1CB513C}" name="Start" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{9367033F-2563-4E51-821F-6AFC1F4705AC}" name="Due" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{D3AF97BC-1639-43D3-9890-6D7CDDE72D03}" name="% Complete" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{C441E3B6-A4F4-4D94-A341-D6AA666ED9A8}" name="Year" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{F7799466-306B-4085-88A3-9BAFC2E2963B}" name="ID" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{515B7545-E5A6-4900-BB7B-2FBE4FB6AAAF}" name="Task"/>
+    <tableColumn id="3" xr3:uid="{B35098B6-DA25-4832-AEA0-570CE5C79917}" name="Owner"/>
+    <tableColumn id="4" xr3:uid="{A2138601-112D-4AC2-B4EE-BE5361088E3A}" name="Department"/>
+    <tableColumn id="5" xr3:uid="{F0814445-79E8-4D6E-834F-EB0C3725F3D6}" name="Status"/>
+    <tableColumn id="6" xr3:uid="{2E7DEBD4-F428-4726-B2CF-4B4DE5C6E0BE}" name="Priority"/>
+    <tableColumn id="7" xr3:uid="{E80337C6-3463-456A-B55A-DCB248D25985}" name="Start" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{5E3602ED-F95C-4854-BA13-F13471ACD221}" name="Due" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{81E0FB5F-7848-475F-8608-DF0EBF9C3069}" name="% Complete" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{5E664E38-2C8D-4F49-88D8-0A7E555C94E1}" name="Year" dataDxfId="12">
       <calculatedColumnFormula>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{75BD1D9A-1359-431B-8208-10A70BE6617D}" name="Notes"/>
+    <tableColumn id="11" xr3:uid="{1DD86DAE-03BB-432E-82AB-37C133F30EC1}" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="AZG Table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1574,1665 +1344,1860 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9500830D-1D1C-4C69-A4C2-1494CA8F5CE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11EDC162-3DBE-44AD-8899-AC75CDC4CA74}">
   <sheetPr>
     <tabColor rgb="FF1F3A5F"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="2.7109375" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="27.7109375" customWidth="1"/>
-    <col min="10" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="14" width="12.7109375" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="2.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="18" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9"/>
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:18" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+    </row>
+    <row r="2" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="11" t="str">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="16" t="str">
         <f ca="1">"As of "&amp;TEXT(TODAY(),"ddd, mmm d, yyyy")&amp;"   |   Pick an owner, status or year: the whole page follows."</f>
         <v>As of Fri, Oct 2, 2026   |   Pick an owner, status or year: the whole page follows.</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-    </row>
-    <row r="3" spans="1:16" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-    </row>
-    <row r="4" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="12" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" spans="1:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C5" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E5" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="12" t="s">
+      <c r="F5" s="20"/>
+      <c r="G5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="H5" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="J4" s="16" t="str">
+      <c r="I5" s="20"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="21" t="str">
         <f>IF(AND(OR(SelOwner="(All)",SelOwner=""),OR(SelStatus="(All)",SelStatus=""),OR(SelYear="(All)",SelYear="")),"Showing all tasks","Filtered view: choose (All) to clear")</f>
         <v>Showing all tasks</v>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-    </row>
-    <row r="5" spans="1:16" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-    </row>
-    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="17" t="s">
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" spans="1:18" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+    </row>
+    <row r="7" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="19" t="s">
+      <c r="C7" s="22"/>
+      <c r="D7" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="23" t="s">
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="25" t="s">
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="31" t="s">
+      <c r="M7" s="22"/>
+      <c r="N7" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="N6" s="32"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="9"/>
-    </row>
-    <row r="7" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="18">
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="6"/>
+    </row>
+    <row r="8" spans="1:18" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="25">
         <f>SUMPRODUCT(InScope)</f>
         <v>42</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="21">
+      <c r="C8" s="24"/>
+      <c r="D8" s="28">
+        <f ca="1">SUMPRODUCT(CondOverdue)</f>
+        <v>7</v>
+      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="31">
+        <f ca="1">SUMPRODUCT(CondFocus)</f>
+        <v>6</v>
+      </c>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="25">
+        <f>SUMPRODUCT(InScope*(Tasks[Status]="In progress"))</f>
+        <v>15</v>
+      </c>
+      <c r="M8" s="24"/>
+      <c r="N8" s="25">
         <f>SUMPRODUCT(InScope*(Tasks[Status]="Done"))</f>
         <v>9</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="24">
-        <f>SUMPRODUCT(InScope*(Tasks[Status]="In progress"))</f>
-        <v>15</v>
-      </c>
-      <c r="I7" s="29"/>
-      <c r="J7" s="28">
-        <f ca="1">SUMPRODUCT(CondOverdue)</f>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="6"/>
+    </row>
+    <row r="9" spans="1:18" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="6"/>
+    </row>
+    <row r="10" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+    </row>
+    <row r="11" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="21" t="str">
+        <f>"Open tasks first, then by due date   |   "&amp;KpiTotal&amp;" match the filters"</f>
+        <v>Open tasks first, then by due date   |   42 match the filters</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="M11" s="6"/>
+      <c r="N11" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+    </row>
+    <row r="12" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="34">
-        <f ca="1">SUMPRODUCT(CondFocus)</f>
-        <v>6</v>
-      </c>
-      <c r="N7" s="35"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="9"/>
-    </row>
-    <row r="8" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="9"/>
-    </row>
-    <row r="9" spans="1:16" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-    </row>
-    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="42" t="s">
+      <c r="C12" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-    </row>
-    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="47" t="s">
+      <c r="E12" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="M12" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="N12" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="O12" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="49" t="s">
+      <c r="P12" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="K11" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="M11" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="N11" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="O11" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="P11" s="9"/>
-    </row>
-    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="50">
+      <c r="Q12" s="18"/>
+      <c r="R12" s="6"/>
+    </row>
+    <row r="13" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="33">
+        <f>IF(Lists!$Q4="","",IF(MOD(INT(Lists!$P4),100000)=99999,"",MOD(INT(Lists!$P4),100000)))</f>
+        <v>46282</v>
+      </c>
+      <c r="C13" s="6" t="str">
+        <f>IF(Lists!$Q4="","No tasks match these filters",INDEX(Tasks[Task],Lists!$Q4)&amp;"")</f>
+        <v>Trade show booth order</v>
+      </c>
+      <c r="D13" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q4="",B13="",F13="Done"),"",IF(B13&lt;TODAY(),"OVERDUE",IF(B13&lt;=TODAY()+6,"This week","")))</f>
+        <v>OVERDUE</v>
+      </c>
+      <c r="E13" s="6" t="str">
+        <f>IF(Lists!$Q4="","",INDEX(Tasks[Owner],Lists!$Q4)&amp;"")</f>
+        <v>Casey L.</v>
+      </c>
+      <c r="F13" s="6" t="str">
+        <f>IF(Lists!$Q4="","",INDEX(Tasks[Status],Lists!$Q4)&amp;"")</f>
+        <v>Blocked</v>
+      </c>
+      <c r="G13" s="6" t="str">
+        <f>IF(Lists!$Q4="","",INDEX(Tasks[Priority],Lists!$Q4)&amp;"")</f>
+        <v>Medium</v>
+      </c>
+      <c r="H13" s="8">
+        <f>IF(Lists!$Q4="","",INDEX(Tasks[% Complete],Lists!$Q4))</f>
+        <v>0.3</v>
+      </c>
+      <c r="I13" s="6">
+        <f>IF(H13="","",H13)</f>
+        <v>0.3</v>
+      </c>
+      <c r="J13" s="6" t="str">
+        <f>IF(Lists!$Q4="","",INDEX(Tasks[Department],Lists!$Q4)&amp;"")</f>
+        <v>Sales</v>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="33">
         <f ca="1">IF(Lists!$I4="","",INT(Lists!$H4))</f>
         <v>46297</v>
       </c>
-      <c r="C12" s="39" t="str">
+      <c r="M13" s="6" t="str">
         <f ca="1">IF(Lists!$I4="","Nothing due in the next 7 days",INDEX(Tasks[Task],Lists!$I4)&amp;"")</f>
         <v>Payroll calendar 2027</v>
       </c>
-      <c r="D12" s="39" t="str">
+      <c r="N13" s="6" t="str">
         <f ca="1">IF(Lists!$I4="","",INDEX(Tasks[Owner],Lists!$I4)&amp;"")</f>
         <v>Jordan M.</v>
       </c>
-      <c r="E12" s="39" t="str">
+      <c r="O13" s="6" t="str">
         <f ca="1">IF(Lists!$I4="","",INDEX(Tasks[Priority],Lists!$I4)&amp;"")</f>
         <v>Medium</v>
       </c>
-      <c r="F12" s="52">
+      <c r="P13" s="8">
         <f ca="1">IF(Lists!$I4="","",INDEX(Tasks[% Complete],Lists!$I4))</f>
         <v>0.9</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="51">
+      <c r="Q13" s="6">
+        <f ca="1">IF(P13="","",P13)</f>
+        <v>0.9</v>
+      </c>
+      <c r="R13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="33">
+        <f>IF(Lists!$Q5="","",IF(MOD(INT(Lists!$P5),100000)=99999,"",MOD(INT(Lists!$P5),100000)))</f>
+        <v>46285</v>
+      </c>
+      <c r="C14" s="6" t="str">
+        <f>IF(Lists!$Q5="","",INDEX(Tasks[Task],Lists!$Q5)&amp;"")</f>
+        <v>Vendor contract renewal</v>
+      </c>
+      <c r="D14" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q5="",B14="",F14="Done"),"",IF(B14&lt;TODAY(),"OVERDUE",IF(B14&lt;=TODAY()+6,"This week","")))</f>
+        <v>OVERDUE</v>
+      </c>
+      <c r="E14" s="6" t="str">
+        <f>IF(Lists!$Q5="","",INDEX(Tasks[Owner],Lists!$Q5)&amp;"")</f>
+        <v>Taylor R.</v>
+      </c>
+      <c r="F14" s="6" t="str">
+        <f>IF(Lists!$Q5="","",INDEX(Tasks[Status],Lists!$Q5)&amp;"")</f>
+        <v>In progress</v>
+      </c>
+      <c r="G14" s="6" t="str">
+        <f>IF(Lists!$Q5="","",INDEX(Tasks[Priority],Lists!$Q5)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="H14" s="8">
+        <f>IF(Lists!$Q5="","",INDEX(Tasks[% Complete],Lists!$Q5))</f>
+        <v>0.7</v>
+      </c>
+      <c r="I14" s="6">
+        <f>IF(H14="","",H14)</f>
+        <v>0.7</v>
+      </c>
+      <c r="J14" s="6" t="str">
+        <f>IF(Lists!$Q5="","",INDEX(Tasks[Department],Lists!$Q5)&amp;"")</f>
+        <v>Operations</v>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="33">
+        <f ca="1">IF(Lists!$I5="","",INT(Lists!$H5))</f>
+        <v>46298</v>
+      </c>
+      <c r="M14" s="6" t="str">
+        <f ca="1">IF(Lists!$I5="","",INDEX(Tasks[Task],Lists!$I5)&amp;"")</f>
+        <v>Warehouse rack labels</v>
+      </c>
+      <c r="N14" s="6" t="str">
+        <f ca="1">IF(Lists!$I5="","",INDEX(Tasks[Owner],Lists!$I5)&amp;"")</f>
+        <v>Avery K.</v>
+      </c>
+      <c r="O14" s="6" t="str">
+        <f ca="1">IF(Lists!$I5="","",INDEX(Tasks[Priority],Lists!$I5)&amp;"")</f>
+        <v>Low</v>
+      </c>
+      <c r="P14" s="8">
+        <f ca="1">IF(Lists!$I5="","",INDEX(Tasks[% Complete],Lists!$I5))</f>
+        <v>0.75</v>
+      </c>
+      <c r="Q14" s="6">
+        <f ca="1">IF(P14="","",P14)</f>
+        <v>0.75</v>
+      </c>
+      <c r="R14" s="6"/>
+    </row>
+    <row r="15" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="33">
+        <f>IF(Lists!$Q6="","",IF(MOD(INT(Lists!$P6),100000)=99999,"",MOD(INT(Lists!$P6),100000)))</f>
+        <v>46289</v>
+      </c>
+      <c r="C15" s="6" t="str">
+        <f>IF(Lists!$Q6="","",INDEX(Tasks[Task],Lists!$Q6)&amp;"")</f>
+        <v>Customer survey mailing</v>
+      </c>
+      <c r="D15" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q6="",B15="",F15="Done"),"",IF(B15&lt;TODAY(),"OVERDUE",IF(B15&lt;=TODAY()+6,"This week","")))</f>
+        <v>OVERDUE</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f>IF(Lists!$Q6="","",INDEX(Tasks[Owner],Lists!$Q6)&amp;"")</f>
+        <v>Casey L.</v>
+      </c>
+      <c r="F15" s="6" t="str">
+        <f>IF(Lists!$Q6="","",INDEX(Tasks[Status],Lists!$Q6)&amp;"")</f>
+        <v>In progress</v>
+      </c>
+      <c r="G15" s="6" t="str">
+        <f>IF(Lists!$Q6="","",INDEX(Tasks[Priority],Lists!$Q6)&amp;"")</f>
+        <v>Medium</v>
+      </c>
+      <c r="H15" s="8">
+        <f>IF(Lists!$Q6="","",INDEX(Tasks[% Complete],Lists!$Q6))</f>
+        <v>0.6</v>
+      </c>
+      <c r="I15" s="6">
+        <f>IF(H15="","",H15)</f>
+        <v>0.6</v>
+      </c>
+      <c r="J15" s="6" t="str">
+        <f>IF(Lists!$Q6="","",INDEX(Tasks[Department],Lists!$Q6)&amp;"")</f>
+        <v>Sales</v>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="33">
+        <f ca="1">IF(Lists!$I6="","",INT(Lists!$H6))</f>
+        <v>46299</v>
+      </c>
+      <c r="M15" s="6" t="str">
+        <f ca="1">IF(Lists!$I6="","",INDEX(Tasks[Task],Lists!$I6)&amp;"")</f>
+        <v>Quote follow-up calls</v>
+      </c>
+      <c r="N15" s="6" t="str">
+        <f ca="1">IF(Lists!$I6="","",INDEX(Tasks[Owner],Lists!$I6)&amp;"")</f>
+        <v>Casey L.</v>
+      </c>
+      <c r="O15" s="6" t="str">
+        <f ca="1">IF(Lists!$I6="","",INDEX(Tasks[Priority],Lists!$I6)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="P15" s="8">
+        <f ca="1">IF(Lists!$I6="","",INDEX(Tasks[% Complete],Lists!$I6))</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="6">
+        <f ca="1">IF(P15="","",P15)</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="6"/>
+    </row>
+    <row r="16" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="33">
+        <f>IF(Lists!$Q7="","",IF(MOD(INT(Lists!$P7),100000)=99999,"",MOD(INT(Lists!$P7),100000)))</f>
+        <v>46291</v>
+      </c>
+      <c r="C16" s="6" t="str">
+        <f>IF(Lists!$Q7="","",INDEX(Tasks[Task],Lists!$Q7)&amp;"")</f>
+        <v>Backup system test</v>
+      </c>
+      <c r="D16" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q7="",B16="",F16="Done"),"",IF(B16&lt;TODAY(),"OVERDUE",IF(B16&lt;=TODAY()+6,"This week","")))</f>
+        <v>OVERDUE</v>
+      </c>
+      <c r="E16" s="6" t="str">
+        <f>IF(Lists!$Q7="","",INDEX(Tasks[Owner],Lists!$Q7)&amp;"")</f>
+        <v>Riley P.</v>
+      </c>
+      <c r="F16" s="6" t="str">
+        <f>IF(Lists!$Q7="","",INDEX(Tasks[Status],Lists!$Q7)&amp;"")</f>
+        <v>Blocked</v>
+      </c>
+      <c r="G16" s="6" t="str">
+        <f>IF(Lists!$Q7="","",INDEX(Tasks[Priority],Lists!$Q7)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="H16" s="8">
+        <f>IF(Lists!$Q7="","",INDEX(Tasks[% Complete],Lists!$Q7))</f>
+        <v>0.4</v>
+      </c>
+      <c r="I16" s="6">
+        <f>IF(H16="","",H16)</f>
+        <v>0.4</v>
+      </c>
+      <c r="J16" s="6" t="str">
+        <f>IF(Lists!$Q7="","",INDEX(Tasks[Department],Lists!$Q7)&amp;"")</f>
+        <v>IT</v>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="33">
+        <f ca="1">IF(Lists!$I7="","",INT(Lists!$H7))</f>
+        <v>46300</v>
+      </c>
+      <c r="M16" s="6" t="str">
+        <f ca="1">IF(Lists!$I7="","",INDEX(Tasks[Task],Lists!$I7)&amp;"")</f>
+        <v>Laptop refresh order</v>
+      </c>
+      <c r="N16" s="6" t="str">
+        <f ca="1">IF(Lists!$I7="","",INDEX(Tasks[Owner],Lists!$I7)&amp;"")</f>
+        <v>Riley P.</v>
+      </c>
+      <c r="O16" s="6" t="str">
+        <f ca="1">IF(Lists!$I7="","",INDEX(Tasks[Priority],Lists!$I7)&amp;"")</f>
+        <v>Medium</v>
+      </c>
+      <c r="P16" s="8">
+        <f ca="1">IF(Lists!$I7="","",INDEX(Tasks[% Complete],Lists!$I7))</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Q16" s="6">
+        <f ca="1">IF(P16="","",P16)</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R16" s="6"/>
+    </row>
+    <row r="17" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="33">
+        <f>IF(Lists!$Q8="","",IF(MOD(INT(Lists!$P8),100000)=99999,"",MOD(INT(Lists!$P8),100000)))</f>
+        <v>46293</v>
+      </c>
+      <c r="C17" s="6" t="str">
+        <f>IF(Lists!$Q8="","",INDEX(Tasks[Task],Lists!$Q8)&amp;"")</f>
+        <v>Expense policy update</v>
+      </c>
+      <c r="D17" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q8="",B17="",F17="Done"),"",IF(B17&lt;TODAY(),"OVERDUE",IF(B17&lt;=TODAY()+6,"This week","")))</f>
+        <v>OVERDUE</v>
+      </c>
+      <c r="E17" s="6" t="str">
+        <f>IF(Lists!$Q8="","",INDEX(Tasks[Owner],Lists!$Q8)&amp;"")</f>
+        <v>Jordan M.</v>
+      </c>
+      <c r="F17" s="6" t="str">
+        <f>IF(Lists!$Q8="","",INDEX(Tasks[Status],Lists!$Q8)&amp;"")</f>
+        <v>In progress</v>
+      </c>
+      <c r="G17" s="6" t="str">
+        <f>IF(Lists!$Q8="","",INDEX(Tasks[Priority],Lists!$Q8)&amp;"")</f>
+        <v>Medium</v>
+      </c>
+      <c r="H17" s="8">
+        <f>IF(Lists!$Q8="","",INDEX(Tasks[% Complete],Lists!$Q8))</f>
+        <v>0.8</v>
+      </c>
+      <c r="I17" s="6">
+        <f>IF(H17="","",H17)</f>
+        <v>0.8</v>
+      </c>
+      <c r="J17" s="6" t="str">
+        <f>IF(Lists!$Q8="","",INDEX(Tasks[Department],Lists!$Q8)&amp;"")</f>
+        <v>Finance</v>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="33">
+        <f ca="1">IF(Lists!$I8="","",INT(Lists!$H8))</f>
+        <v>46302</v>
+      </c>
+      <c r="M17" s="6" t="str">
+        <f ca="1">IF(Lists!$I8="","",INDEX(Tasks[Task],Lists!$I8)&amp;"")</f>
+        <v>Benefits enrollment memo</v>
+      </c>
+      <c r="N17" s="6" t="str">
+        <f ca="1">IF(Lists!$I8="","",INDEX(Tasks[Owner],Lists!$I8)&amp;"")</f>
+        <v>Morgan T.</v>
+      </c>
+      <c r="O17" s="6" t="str">
+        <f ca="1">IF(Lists!$I8="","",INDEX(Tasks[Priority],Lists!$I8)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="P17" s="8">
+        <f ca="1">IF(Lists!$I8="","",INDEX(Tasks[% Complete],Lists!$I8))</f>
+        <v>0.35</v>
+      </c>
+      <c r="Q17" s="6">
+        <f ca="1">IF(P17="","",P17)</f>
+        <v>0.35</v>
+      </c>
+      <c r="R17" s="6"/>
+    </row>
+    <row r="18" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="33">
+        <f>IF(Lists!$Q9="","",IF(MOD(INT(Lists!$P9),100000)=99999,"",MOD(INT(Lists!$P9),100000)))</f>
+        <v>46295</v>
+      </c>
+      <c r="C18" s="6" t="str">
+        <f>IF(Lists!$Q9="","",INDEX(Tasks[Task],Lists!$Q9)&amp;"")</f>
+        <v>Safety training sign-off</v>
+      </c>
+      <c r="D18" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q9="",B18="",F18="Done"),"",IF(B18&lt;TODAY(),"OVERDUE",IF(B18&lt;=TODAY()+6,"This week","")))</f>
+        <v>OVERDUE</v>
+      </c>
+      <c r="E18" s="6" t="str">
+        <f>IF(Lists!$Q9="","",INDEX(Tasks[Owner],Lists!$Q9)&amp;"")</f>
+        <v>Morgan T.</v>
+      </c>
+      <c r="F18" s="6" t="str">
+        <f>IF(Lists!$Q9="","",INDEX(Tasks[Status],Lists!$Q9)&amp;"")</f>
+        <v>Not started</v>
+      </c>
+      <c r="G18" s="6" t="str">
+        <f>IF(Lists!$Q9="","",INDEX(Tasks[Priority],Lists!$Q9)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="H18" s="8">
+        <f>IF(Lists!$Q9="","",INDEX(Tasks[% Complete],Lists!$Q9))</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="6">
+        <f>IF(H18="","",H18)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="6" t="str">
+        <f>IF(Lists!$Q9="","",INDEX(Tasks[Department],Lists!$Q9)&amp;"")</f>
+        <v>HR</v>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="33">
+        <f ca="1">IF(Lists!$I9="","",INT(Lists!$H9))</f>
+        <v>46303</v>
+      </c>
+      <c r="M18" s="6" t="str">
+        <f ca="1">IF(Lists!$I9="","",INDEX(Tasks[Task],Lists!$I9)&amp;"")</f>
+        <v>Fleet insurance renewal</v>
+      </c>
+      <c r="N18" s="6" t="str">
+        <f ca="1">IF(Lists!$I9="","",INDEX(Tasks[Owner],Lists!$I9)&amp;"")</f>
+        <v>Taylor R.</v>
+      </c>
+      <c r="O18" s="6" t="str">
+        <f ca="1">IF(Lists!$I9="","",INDEX(Tasks[Priority],Lists!$I9)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="P18" s="8">
+        <f ca="1">IF(Lists!$I9="","",INDEX(Tasks[% Complete],Lists!$I9))</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6">
+        <f ca="1">IF(P18="","",P18)</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="6"/>
+    </row>
+    <row r="19" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="33">
+        <f>IF(Lists!$Q10="","",IF(MOD(INT(Lists!$P10),100000)=99999,"",MOD(INT(Lists!$P10),100000)))</f>
+        <v>46296</v>
+      </c>
+      <c r="C19" s="6" t="str">
+        <f>IF(Lists!$Q10="","",INDEX(Tasks[Task],Lists!$Q10)&amp;"")</f>
+        <v>Forklift inspection</v>
+      </c>
+      <c r="D19" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q10="",B19="",F19="Done"),"",IF(B19&lt;TODAY(),"OVERDUE",IF(B19&lt;=TODAY()+6,"This week","")))</f>
+        <v>OVERDUE</v>
+      </c>
+      <c r="E19" s="6" t="str">
+        <f>IF(Lists!$Q10="","",INDEX(Tasks[Owner],Lists!$Q10)&amp;"")</f>
+        <v>Avery K.</v>
+      </c>
+      <c r="F19" s="6" t="str">
+        <f>IF(Lists!$Q10="","",INDEX(Tasks[Status],Lists!$Q10)&amp;"")</f>
+        <v>In progress</v>
+      </c>
+      <c r="G19" s="6" t="str">
+        <f>IF(Lists!$Q10="","",INDEX(Tasks[Priority],Lists!$Q10)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="H19" s="8">
+        <f>IF(Lists!$Q10="","",INDEX(Tasks[% Complete],Lists!$Q10))</f>
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="6">
+        <f>IF(H19="","",H19)</f>
+        <v>0.5</v>
+      </c>
+      <c r="J19" s="6" t="str">
+        <f>IF(Lists!$Q10="","",INDEX(Tasks[Department],Lists!$Q10)&amp;"")</f>
+        <v>Operations</v>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="33" t="str">
+        <f ca="1">IF(Lists!$I10="","",INT(Lists!$H10))</f>
+        <v/>
+      </c>
+      <c r="M19" s="6" t="str">
+        <f ca="1">IF(Lists!$I10="","",INDEX(Tasks[Task],Lists!$I10)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="N19" s="6" t="str">
+        <f ca="1">IF(Lists!$I10="","",INDEX(Tasks[Owner],Lists!$I10)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="O19" s="6" t="str">
+        <f ca="1">IF(Lists!$I10="","",INDEX(Tasks[Priority],Lists!$I10)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="8" t="str">
+        <f ca="1">IF(Lists!$I10="","",INDEX(Tasks[% Complete],Lists!$I10))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="str">
+        <f ca="1">IF(P19="","",P19)</f>
+        <v/>
+      </c>
+      <c r="R19" s="6"/>
+    </row>
+    <row r="20" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="33">
+        <f>IF(Lists!$Q11="","",IF(MOD(INT(Lists!$P11),100000)=99999,"",MOD(INT(Lists!$P11),100000)))</f>
+        <v>46297</v>
+      </c>
+      <c r="C20" s="6" t="str">
+        <f>IF(Lists!$Q11="","",INDEX(Tasks[Task],Lists!$Q11)&amp;"")</f>
+        <v>Payroll calendar 2027</v>
+      </c>
+      <c r="D20" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q11="",B20="",F20="Done"),"",IF(B20&lt;TODAY(),"OVERDUE",IF(B20&lt;=TODAY()+6,"This week","")))</f>
+        <v>This week</v>
+      </c>
+      <c r="E20" s="6" t="str">
+        <f>IF(Lists!$Q11="","",INDEX(Tasks[Owner],Lists!$Q11)&amp;"")</f>
+        <v>Jordan M.</v>
+      </c>
+      <c r="F20" s="6" t="str">
+        <f>IF(Lists!$Q11="","",INDEX(Tasks[Status],Lists!$Q11)&amp;"")</f>
+        <v>In progress</v>
+      </c>
+      <c r="G20" s="6" t="str">
+        <f>IF(Lists!$Q11="","",INDEX(Tasks[Priority],Lists!$Q11)&amp;"")</f>
+        <v>Medium</v>
+      </c>
+      <c r="H20" s="8">
+        <f>IF(Lists!$Q11="","",INDEX(Tasks[% Complete],Lists!$Q11))</f>
+        <v>0.9</v>
+      </c>
+      <c r="I20" s="6">
+        <f>IF(H20="","",H20)</f>
+        <v>0.9</v>
+      </c>
+      <c r="J20" s="6" t="str">
+        <f>IF(Lists!$Q11="","",INDEX(Tasks[Department],Lists!$Q11)&amp;"")</f>
+        <v>Finance</v>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="33" t="str">
+        <f ca="1">IF(Lists!$I11="","",INT(Lists!$H11))</f>
+        <v/>
+      </c>
+      <c r="M20" s="6" t="str">
+        <f ca="1">IF(Lists!$I11="","",INDEX(Tasks[Task],Lists!$I11)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="N20" s="6" t="str">
+        <f ca="1">IF(Lists!$I11="","",INDEX(Tasks[Owner],Lists!$I11)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="O20" s="6" t="str">
+        <f ca="1">IF(Lists!$I11="","",INDEX(Tasks[Priority],Lists!$I11)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="8" t="str">
+        <f ca="1">IF(Lists!$I11="","",INDEX(Tasks[% Complete],Lists!$I11))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="str">
+        <f ca="1">IF(P20="","",P20)</f>
+        <v/>
+      </c>
+      <c r="R20" s="6"/>
+    </row>
+    <row r="21" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="33">
+        <f>IF(Lists!$Q12="","",IF(MOD(INT(Lists!$P12),100000)=99999,"",MOD(INT(Lists!$P12),100000)))</f>
+        <v>46298</v>
+      </c>
+      <c r="C21" s="6" t="str">
+        <f>IF(Lists!$Q12="","",INDEX(Tasks[Task],Lists!$Q12)&amp;"")</f>
+        <v>Warehouse rack labels</v>
+      </c>
+      <c r="D21" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q12="",B21="",F21="Done"),"",IF(B21&lt;TODAY(),"OVERDUE",IF(B21&lt;=TODAY()+6,"This week","")))</f>
+        <v>This week</v>
+      </c>
+      <c r="E21" s="6" t="str">
+        <f>IF(Lists!$Q12="","",INDEX(Tasks[Owner],Lists!$Q12)&amp;"")</f>
+        <v>Avery K.</v>
+      </c>
+      <c r="F21" s="6" t="str">
+        <f>IF(Lists!$Q12="","",INDEX(Tasks[Status],Lists!$Q12)&amp;"")</f>
+        <v>In progress</v>
+      </c>
+      <c r="G21" s="6" t="str">
+        <f>IF(Lists!$Q12="","",INDEX(Tasks[Priority],Lists!$Q12)&amp;"")</f>
+        <v>Low</v>
+      </c>
+      <c r="H21" s="8">
+        <f>IF(Lists!$Q12="","",INDEX(Tasks[% Complete],Lists!$Q12))</f>
+        <v>0.75</v>
+      </c>
+      <c r="I21" s="6">
+        <f>IF(H21="","",H21)</f>
+        <v>0.75</v>
+      </c>
+      <c r="J21" s="6" t="str">
+        <f>IF(Lists!$Q12="","",INDEX(Tasks[Department],Lists!$Q12)&amp;"")</f>
+        <v>Operations</v>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="21" t="str">
+        <f ca="1">IF(KpiDueThisWeek&gt;8,"+ "&amp;(KpiDueThisWeek-8)&amp;" more not shown","")</f>
+        <v/>
+      </c>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+    </row>
+    <row r="22" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="33">
+        <f>IF(Lists!$Q13="","",IF(MOD(INT(Lists!$P13),100000)=99999,"",MOD(INT(Lists!$P13),100000)))</f>
+        <v>46299</v>
+      </c>
+      <c r="C22" s="6" t="str">
+        <f>IF(Lists!$Q13="","",INDEX(Tasks[Task],Lists!$Q13)&amp;"")</f>
+        <v>Quote follow-up calls</v>
+      </c>
+      <c r="D22" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q13="",B22="",F22="Done"),"",IF(B22&lt;TODAY(),"OVERDUE",IF(B22&lt;=TODAY()+6,"This week","")))</f>
+        <v>This week</v>
+      </c>
+      <c r="E22" s="6" t="str">
+        <f>IF(Lists!$Q13="","",INDEX(Tasks[Owner],Lists!$Q13)&amp;"")</f>
+        <v>Casey L.</v>
+      </c>
+      <c r="F22" s="6" t="str">
+        <f>IF(Lists!$Q13="","",INDEX(Tasks[Status],Lists!$Q13)&amp;"")</f>
+        <v>Not started</v>
+      </c>
+      <c r="G22" s="6" t="str">
+        <f>IF(Lists!$Q13="","",INDEX(Tasks[Priority],Lists!$Q13)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="H22" s="8">
+        <f>IF(Lists!$Q13="","",INDEX(Tasks[% Complete],Lists!$Q13))</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="6">
+        <f>IF(H22="","",H22)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="6" t="str">
+        <f>IF(Lists!$Q13="","",INDEX(Tasks[Department],Lists!$Q13)&amp;"")</f>
+        <v>Sales</v>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+    </row>
+    <row r="23" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="33">
+        <f>IF(Lists!$Q14="","",IF(MOD(INT(Lists!$P14),100000)=99999,"",MOD(INT(Lists!$P14),100000)))</f>
+        <v>46300</v>
+      </c>
+      <c r="C23" s="6" t="str">
+        <f>IF(Lists!$Q14="","",INDEX(Tasks[Task],Lists!$Q14)&amp;"")</f>
+        <v>Laptop refresh order</v>
+      </c>
+      <c r="D23" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q14="",B23="",F23="Done"),"",IF(B23&lt;TODAY(),"OVERDUE",IF(B23&lt;=TODAY()+6,"This week","")))</f>
+        <v>This week</v>
+      </c>
+      <c r="E23" s="6" t="str">
+        <f>IF(Lists!$Q14="","",INDEX(Tasks[Owner],Lists!$Q14)&amp;"")</f>
+        <v>Riley P.</v>
+      </c>
+      <c r="F23" s="6" t="str">
+        <f>IF(Lists!$Q14="","",INDEX(Tasks[Status],Lists!$Q14)&amp;"")</f>
+        <v>In progress</v>
+      </c>
+      <c r="G23" s="6" t="str">
+        <f>IF(Lists!$Q14="","",INDEX(Tasks[Priority],Lists!$Q14)&amp;"")</f>
+        <v>Medium</v>
+      </c>
+      <c r="H23" s="8">
+        <f>IF(Lists!$Q14="","",INDEX(Tasks[% Complete],Lists!$Q14))</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I23" s="6">
+        <f>IF(H23="","",H23)</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J23" s="6" t="str">
+        <f>IF(Lists!$Q14="","",INDEX(Tasks[Department],Lists!$Q14)&amp;"")</f>
+        <v>IT</v>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="M23" s="6"/>
+      <c r="N23" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+    </row>
+    <row r="24" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="33">
+        <f>IF(Lists!$Q15="","",IF(MOD(INT(Lists!$P15),100000)=99999,"",MOD(INT(Lists!$P15),100000)))</f>
+        <v>46302</v>
+      </c>
+      <c r="C24" s="6" t="str">
+        <f>IF(Lists!$Q15="","",INDEX(Tasks[Task],Lists!$Q15)&amp;"")</f>
+        <v>Benefits enrollment memo</v>
+      </c>
+      <c r="D24" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q15="",B24="",F24="Done"),"",IF(B24&lt;TODAY(),"OVERDUE",IF(B24&lt;=TODAY()+6,"This week","")))</f>
+        <v>This week</v>
+      </c>
+      <c r="E24" s="6" t="str">
+        <f>IF(Lists!$Q15="","",INDEX(Tasks[Owner],Lists!$Q15)&amp;"")</f>
+        <v>Morgan T.</v>
+      </c>
+      <c r="F24" s="6" t="str">
+        <f>IF(Lists!$Q15="","",INDEX(Tasks[Status],Lists!$Q15)&amp;"")</f>
+        <v>In progress</v>
+      </c>
+      <c r="G24" s="6" t="str">
+        <f>IF(Lists!$Q15="","",INDEX(Tasks[Priority],Lists!$Q15)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="H24" s="8">
+        <f>IF(Lists!$Q15="","",INDEX(Tasks[% Complete],Lists!$Q15))</f>
+        <v>0.35</v>
+      </c>
+      <c r="I24" s="6">
+        <f>IF(H24="","",H24)</f>
+        <v>0.35</v>
+      </c>
+      <c r="J24" s="6" t="str">
+        <f>IF(Lists!$Q15="","",INDEX(Tasks[Department],Lists!$Q15)&amp;"")</f>
+        <v>HR</v>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="M24" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="P24" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q24" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="R24" s="6"/>
+    </row>
+    <row r="25" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6"/>
+      <c r="B25" s="33">
+        <f>IF(Lists!$Q16="","",IF(MOD(INT(Lists!$P16),100000)=99999,"",MOD(INT(Lists!$P16),100000)))</f>
+        <v>46303</v>
+      </c>
+      <c r="C25" s="6" t="str">
+        <f>IF(Lists!$Q16="","",INDEX(Tasks[Task],Lists!$Q16)&amp;"")</f>
+        <v>Fleet insurance renewal</v>
+      </c>
+      <c r="D25" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q16="",B25="",F25="Done"),"",IF(B25&lt;TODAY(),"OVERDUE",IF(B25&lt;=TODAY()+6,"This week","")))</f>
+        <v>This week</v>
+      </c>
+      <c r="E25" s="6" t="str">
+        <f>IF(Lists!$Q16="","",INDEX(Tasks[Owner],Lists!$Q16)&amp;"")</f>
+        <v>Taylor R.</v>
+      </c>
+      <c r="F25" s="6" t="str">
+        <f>IF(Lists!$Q16="","",INDEX(Tasks[Status],Lists!$Q16)&amp;"")</f>
+        <v>Not started</v>
+      </c>
+      <c r="G25" s="6" t="str">
+        <f>IF(Lists!$Q16="","",INDEX(Tasks[Priority],Lists!$Q16)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="H25" s="8">
+        <f>IF(Lists!$Q16="","",INDEX(Tasks[% Complete],Lists!$Q16))</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="6">
+        <f>IF(H25="","",H25)</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="6" t="str">
+        <f>IF(Lists!$Q16="","",INDEX(Tasks[Department],Lists!$Q16)&amp;"")</f>
+        <v>Operations</v>
+      </c>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6" t="str">
+        <f>IF(Lists!$A5="","",Lists!$A5)</f>
+        <v>Avery K.</v>
+      </c>
+      <c r="M25" s="6">
+        <f>IF(N25="","",N25)</f>
+        <v>0.31</v>
+      </c>
+      <c r="N25" s="36">
+        <f>IF(OR(L25="",O25=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=L25)*Tasks[% Complete])/O25)</f>
+        <v>0.31</v>
+      </c>
+      <c r="O25" s="9">
+        <f>IF(L25="","",SUMPRODUCT(InScope*(Tasks[Owner]=L25)))</f>
+        <v>5</v>
+      </c>
+      <c r="P25" s="9">
+        <f>IF(L25="","",SUMPRODUCT(InScope*(Tasks[Owner]=L25)*(Tasks[Status]="Done")))</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="9">
+        <f ca="1">IF(L25="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=L25)))</f>
+        <v>1</v>
+      </c>
+      <c r="R25" s="6"/>
+    </row>
+    <row r="26" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6"/>
+      <c r="B26" s="33">
+        <f>IF(Lists!$Q17="","",IF(MOD(INT(Lists!$P17),100000)=99999,"",MOD(INT(Lists!$P17),100000)))</f>
+        <v>46304</v>
+      </c>
+      <c r="C26" s="6" t="str">
+        <f>IF(Lists!$Q17="","",INDEX(Tasks[Task],Lists!$Q17)&amp;"")</f>
+        <v>Budget draft for 2027</v>
+      </c>
+      <c r="D26" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q17="",B26="",F26="Done"),"",IF(B26&lt;TODAY(),"OVERDUE",IF(B26&lt;=TODAY()+6,"This week","")))</f>
+        <v/>
+      </c>
+      <c r="E26" s="6" t="str">
+        <f>IF(Lists!$Q17="","",INDEX(Tasks[Owner],Lists!$Q17)&amp;"")</f>
+        <v>Jordan M.</v>
+      </c>
+      <c r="F26" s="6" t="str">
+        <f>IF(Lists!$Q17="","",INDEX(Tasks[Status],Lists!$Q17)&amp;"")</f>
+        <v>In progress</v>
+      </c>
+      <c r="G26" s="6" t="str">
+        <f>IF(Lists!$Q17="","",INDEX(Tasks[Priority],Lists!$Q17)&amp;"")</f>
+        <v>High</v>
+      </c>
+      <c r="H26" s="8">
+        <f>IF(Lists!$Q17="","",INDEX(Tasks[% Complete],Lists!$Q17))</f>
+        <v>0.45</v>
+      </c>
+      <c r="I26" s="6">
+        <f>IF(H26="","",H26)</f>
+        <v>0.45</v>
+      </c>
+      <c r="J26" s="6" t="str">
+        <f>IF(Lists!$Q17="","",INDEX(Tasks[Department],Lists!$Q17)&amp;"")</f>
+        <v>Finance</v>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6" t="str">
+        <f>IF(Lists!$A6="","",Lists!$A6)</f>
+        <v>Casey L.</v>
+      </c>
+      <c r="M26" s="6">
+        <f>IF(N26="","",N26)</f>
+        <v>0.37777777777777782</v>
+      </c>
+      <c r="N26" s="36">
+        <f>IF(OR(L26="",O26=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=L26)*Tasks[% Complete])/O26)</f>
+        <v>0.37777777777777782</v>
+      </c>
+      <c r="O26" s="9">
+        <f>IF(L26="","",SUMPRODUCT(InScope*(Tasks[Owner]=L26)))</f>
+        <v>9</v>
+      </c>
+      <c r="P26" s="9">
+        <f>IF(L26="","",SUMPRODUCT(InScope*(Tasks[Owner]=L26)*(Tasks[Status]="Done")))</f>
+        <v>2</v>
+      </c>
+      <c r="Q26" s="9">
+        <f ca="1">IF(L26="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=L26)))</f>
+        <v>2</v>
+      </c>
+      <c r="R26" s="6"/>
+    </row>
+    <row r="27" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="33">
+        <f>IF(Lists!$Q18="","",IF(MOD(INT(Lists!$P18),100000)=99999,"",MOD(INT(Lists!$P18),100000)))</f>
+        <v>46305</v>
+      </c>
+      <c r="C27" s="6" t="str">
+        <f>IF(Lists!$Q18="","",INDEX(Tasks[Task],Lists!$Q18)&amp;"")</f>
+        <v>Website contact form fix</v>
+      </c>
+      <c r="D27" s="9" t="str">
+        <f ca="1">IF(OR(Lists!$Q18="",B27="",F27="Done"),"",IF(B27&lt;TODAY(),"OVERDUE",IF(B27&lt;=TODAY()+6,"This week","")))</f>
+        <v/>
+      </c>
+      <c r="E27" s="6" t="str">
+        <f>IF(Lists!$Q18="","",INDEX(Tasks[Owner],Lists!$Q18)&amp;"")</f>
+        <v>Riley P.</v>
+      </c>
+      <c r="F27" s="6" t="str">
+        <f>IF(Lists!$Q18="","",INDEX(Tasks[Status],Lists!$Q18)&amp;"")</f>
+        <v>Not started</v>
+      </c>
+      <c r="G27" s="6" t="str">
+        <f>IF(Lists!$Q18="","",INDEX(Tasks[Priority],Lists!$Q18)&amp;"")</f>
+        <v>Medium</v>
+      </c>
+      <c r="H27" s="8">
+        <f>IF(Lists!$Q18="","",INDEX(Tasks[% Complete],Lists!$Q18))</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="6">
+        <f>IF(H27="","",H27)</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="6" t="str">
+        <f>IF(Lists!$Q18="","",INDEX(Tasks[Department],Lists!$Q18)&amp;"")</f>
+        <v>IT</v>
+      </c>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6" t="str">
+        <f>IF(Lists!$A7="","",Lists!$A7)</f>
+        <v>Jordan M.</v>
+      </c>
+      <c r="M27" s="6">
+        <f>IF(N27="","",N27)</f>
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="N27" s="36">
+        <f>IF(OR(L27="",O27=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=L27)*Tasks[% Complete])/O27)</f>
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="O27" s="9">
+        <f>IF(L27="","",SUMPRODUCT(InScope*(Tasks[Owner]=L27)))</f>
+        <v>8</v>
+      </c>
+      <c r="P27" s="9">
+        <f>IF(L27="","",SUMPRODUCT(InScope*(Tasks[Owner]=L27)*(Tasks[Status]="Done")))</f>
+        <v>2</v>
+      </c>
+      <c r="Q27" s="9">
+        <f ca="1">IF(L27="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=L27)))</f>
+        <v>1</v>
+      </c>
+      <c r="R27" s="6"/>
+    </row>
+    <row r="28" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6"/>
+      <c r="B28" s="21" t="str">
+        <f>IF(KpiTotal&gt;15,"+ "&amp;(KpiTotal-15)&amp;" more not shown","")</f>
+        <v>+ 27 more not shown</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6" t="str">
+        <f>IF(Lists!$A8="","",Lists!$A8)</f>
+        <v>Morgan T.</v>
+      </c>
+      <c r="M28" s="6">
+        <f>IF(N28="","",N28)</f>
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="N28" s="36">
+        <f>IF(OR(L28="",O28=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=L28)*Tasks[% Complete])/O28)</f>
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="O28" s="9">
+        <f>IF(L28="","",SUMPRODUCT(InScope*(Tasks[Owner]=L28)))</f>
+        <v>7</v>
+      </c>
+      <c r="P28" s="9">
+        <f>IF(L28="","",SUMPRODUCT(InScope*(Tasks[Owner]=L28)*(Tasks[Status]="Done")))</f>
+        <v>2</v>
+      </c>
+      <c r="Q28" s="9">
+        <f ca="1">IF(L28="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=L28)))</f>
+        <v>1</v>
+      </c>
+      <c r="R28" s="6"/>
+    </row>
+    <row r="29" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6" t="str">
+        <f>IF(Lists!$A9="","",Lists!$A9)</f>
+        <v>Riley P.</v>
+      </c>
+      <c r="M29" s="6">
+        <f>IF(N29="","",N29)</f>
+        <v>0.41875000000000001</v>
+      </c>
+      <c r="N29" s="36">
+        <f>IF(OR(L29="",O29=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=L29)*Tasks[% Complete])/O29)</f>
+        <v>0.41875000000000001</v>
+      </c>
+      <c r="O29" s="9">
+        <f>IF(L29="","",SUMPRODUCT(InScope*(Tasks[Owner]=L29)))</f>
+        <v>8</v>
+      </c>
+      <c r="P29" s="9">
+        <f>IF(L29="","",SUMPRODUCT(InScope*(Tasks[Owner]=L29)*(Tasks[Status]="Done")))</f>
+        <v>2</v>
+      </c>
+      <c r="Q29" s="9">
+        <f ca="1">IF(L29="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=L29)))</f>
+        <v>1</v>
+      </c>
+      <c r="R29" s="6"/>
+    </row>
+    <row r="30" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
+      <c r="B30" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6" t="str">
+        <f>IF(Lists!$A10="","",Lists!$A10)</f>
+        <v>Taylor R.</v>
+      </c>
+      <c r="M30" s="6">
+        <f>IF(N30="","",N30)</f>
+        <v>0.42000000000000004</v>
+      </c>
+      <c r="N30" s="36">
+        <f>IF(OR(L30="",O30=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=L30)*Tasks[% Complete])/O30)</f>
+        <v>0.42000000000000004</v>
+      </c>
+      <c r="O30" s="9">
+        <f>IF(L30="","",SUMPRODUCT(InScope*(Tasks[Owner]=L30)))</f>
+        <v>5</v>
+      </c>
+      <c r="P30" s="9">
+        <f>IF(L30="","",SUMPRODUCT(InScope*(Tasks[Owner]=L30)*(Tasks[Status]="Done")))</f>
+        <v>1</v>
+      </c>
+      <c r="Q30" s="9">
+        <f ca="1">IF(L30="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=L30)))</f>
+        <v>1</v>
+      </c>
+      <c r="R30" s="6"/>
+    </row>
+    <row r="31" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6" t="str">
+        <f>IF(Lists!$A11="","",Lists!$A11)</f>
+        <v/>
+      </c>
+      <c r="M31" s="6" t="str">
+        <f>IF(N31="","",N31)</f>
+        <v/>
+      </c>
+      <c r="N31" s="36" t="str">
+        <f>IF(OR(L31="",O31=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=L31)*Tasks[% Complete])/O31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="9" t="str">
+        <f>IF(L31="","",SUMPRODUCT(InScope*(Tasks[Owner]=L31)))</f>
+        <v/>
+      </c>
+      <c r="P31" s="9" t="str">
+        <f>IF(L31="","",SUMPRODUCT(InScope*(Tasks[Owner]=L31)*(Tasks[Status]="Done")))</f>
+        <v/>
+      </c>
+      <c r="Q31" s="9" t="str">
+        <f>IF(L31="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=L31)))</f>
+        <v/>
+      </c>
+      <c r="R31" s="6"/>
+    </row>
+    <row r="32" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="33">
         <f ca="1">IF(Lists!$M4="","",INT(Lists!$L4))</f>
         <v>46297</v>
       </c>
-      <c r="I12" s="9" t="str">
+      <c r="C32" s="6" t="str">
         <f ca="1">IF(Lists!$M4="","Nothing coming up",INDEX(Tasks[Task],Lists!$M4)&amp;"")</f>
         <v>Payroll calendar 2027</v>
       </c>
-      <c r="J12" s="9" t="str">
+      <c r="D32" s="37">
+        <f ca="1">IF(Lists!$M4="","",INT(Lists!$L4)-TODAY())</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="str">
         <f ca="1">IF(Lists!$M4="","",INDEX(Tasks[Owner],Lists!$M4)&amp;"")</f>
         <v>Jordan M.</v>
       </c>
-      <c r="K12" s="9" t="str">
+      <c r="F32" s="6" t="str">
         <f ca="1">IF(Lists!$M4="","",INDEX(Tasks[Status],Lists!$M4)&amp;"")</f>
         <v>In progress</v>
       </c>
-      <c r="L12" s="9" t="str">
+      <c r="G32" s="6" t="str">
         <f ca="1">IF(Lists!$M4="","",INDEX(Tasks[Priority],Lists!$M4)&amp;"")</f>
         <v>Medium</v>
       </c>
-      <c r="M12" s="53">
+      <c r="H32" s="8">
         <f ca="1">IF(Lists!$M4="","",INDEX(Tasks[% Complete],Lists!$M4))</f>
         <v>0.9</v>
       </c>
-      <c r="N12" s="54">
-        <f ca="1">IF(Lists!$M4="","",INT(Lists!$L4)-TODAY())</f>
-        <v>0</v>
-      </c>
-      <c r="O12" s="9" t="str">
+      <c r="I32" s="6">
+        <f ca="1">IF(H32="","",H32)</f>
+        <v>0.9</v>
+      </c>
+      <c r="J32" s="6" t="str">
         <f ca="1">IF(Lists!$M4="","",INDEX(Tasks[Department],Lists!$M4)&amp;"")</f>
         <v>Finance</v>
       </c>
-      <c r="P12" s="9"/>
-    </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="50">
-        <f ca="1">IF(Lists!$I5="","",INT(Lists!$H5))</f>
-        <v>46298</v>
-      </c>
-      <c r="C13" s="39" t="str">
-        <f ca="1">IF(Lists!$I5="","",INDEX(Tasks[Task],Lists!$I5)&amp;"")</f>
-        <v>Warehouse rack labels</v>
-      </c>
-      <c r="D13" s="39" t="str">
-        <f ca="1">IF(Lists!$I5="","",INDEX(Tasks[Owner],Lists!$I5)&amp;"")</f>
-        <v>Avery K.</v>
-      </c>
-      <c r="E13" s="39" t="str">
-        <f ca="1">IF(Lists!$I5="","",INDEX(Tasks[Priority],Lists!$I5)&amp;"")</f>
-        <v>Low</v>
-      </c>
-      <c r="F13" s="52">
-        <f ca="1">IF(Lists!$I5="","",INDEX(Tasks[% Complete],Lists!$I5))</f>
-        <v>0.75</v>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="51">
+      <c r="K32" s="6"/>
+      <c r="L32" s="6" t="str">
+        <f>IF(Lists!$A12="","",Lists!$A12)</f>
+        <v/>
+      </c>
+      <c r="M32" s="6" t="str">
+        <f>IF(N32="","",N32)</f>
+        <v/>
+      </c>
+      <c r="N32" s="36" t="str">
+        <f>IF(OR(L32="",O32=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=L32)*Tasks[% Complete])/O32)</f>
+        <v/>
+      </c>
+      <c r="O32" s="9" t="str">
+        <f>IF(L32="","",SUMPRODUCT(InScope*(Tasks[Owner]=L32)))</f>
+        <v/>
+      </c>
+      <c r="P32" s="9" t="str">
+        <f>IF(L32="","",SUMPRODUCT(InScope*(Tasks[Owner]=L32)*(Tasks[Status]="Done")))</f>
+        <v/>
+      </c>
+      <c r="Q32" s="9" t="str">
+        <f>IF(L32="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=L32)))</f>
+        <v/>
+      </c>
+      <c r="R32" s="6"/>
+    </row>
+    <row r="33" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="33">
         <f ca="1">IF(Lists!$M5="","",INT(Lists!$L5))</f>
         <v>46298</v>
       </c>
-      <c r="I13" s="9" t="str">
+      <c r="C33" s="6" t="str">
         <f ca="1">IF(Lists!$M5="","",INDEX(Tasks[Task],Lists!$M5)&amp;"")</f>
         <v>Warehouse rack labels</v>
       </c>
-      <c r="J13" s="9" t="str">
+      <c r="D33" s="37">
+        <f ca="1">IF(Lists!$M5="","",INT(Lists!$L5)-TODAY())</f>
+        <v>1</v>
+      </c>
+      <c r="E33" s="6" t="str">
         <f ca="1">IF(Lists!$M5="","",INDEX(Tasks[Owner],Lists!$M5)&amp;"")</f>
         <v>Avery K.</v>
       </c>
-      <c r="K13" s="9" t="str">
+      <c r="F33" s="6" t="str">
         <f ca="1">IF(Lists!$M5="","",INDEX(Tasks[Status],Lists!$M5)&amp;"")</f>
         <v>In progress</v>
       </c>
-      <c r="L13" s="9" t="str">
+      <c r="G33" s="6" t="str">
         <f ca="1">IF(Lists!$M5="","",INDEX(Tasks[Priority],Lists!$M5)&amp;"")</f>
         <v>Low</v>
       </c>
-      <c r="M13" s="53">
+      <c r="H33" s="8">
         <f ca="1">IF(Lists!$M5="","",INDEX(Tasks[% Complete],Lists!$M5))</f>
         <v>0.75</v>
       </c>
-      <c r="N13" s="54">
-        <f ca="1">IF(Lists!$M5="","",INT(Lists!$L5)-TODAY())</f>
-        <v>1</v>
-      </c>
-      <c r="O13" s="9" t="str">
+      <c r="I33" s="6">
+        <f ca="1">IF(H33="","",H33)</f>
+        <v>0.75</v>
+      </c>
+      <c r="J33" s="6" t="str">
         <f ca="1">IF(Lists!$M5="","",INDEX(Tasks[Department],Lists!$M5)&amp;"")</f>
         <v>Operations</v>
       </c>
-      <c r="P13" s="9"/>
-    </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="50">
-        <f ca="1">IF(Lists!$I6="","",INT(Lists!$H6))</f>
-        <v>46299</v>
-      </c>
-      <c r="C14" s="39" t="str">
-        <f ca="1">IF(Lists!$I6="","",INDEX(Tasks[Task],Lists!$I6)&amp;"")</f>
-        <v>Quote follow-up calls</v>
-      </c>
-      <c r="D14" s="39" t="str">
-        <f ca="1">IF(Lists!$I6="","",INDEX(Tasks[Owner],Lists!$I6)&amp;"")</f>
-        <v>Casey L.</v>
-      </c>
-      <c r="E14" s="39" t="str">
-        <f ca="1">IF(Lists!$I6="","",INDEX(Tasks[Priority],Lists!$I6)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="F14" s="52">
-        <f ca="1">IF(Lists!$I6="","",INDEX(Tasks[% Complete],Lists!$I6))</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="51">
+      <c r="K33" s="6"/>
+      <c r="L33" s="21" t="str">
+        <f>IF(COUNTIF(Lists!$A$5:$A$34,"?*")&gt;8,"+ "&amp;(COUNTIF(Lists!$A$5:$A$34,"?*")-8)&amp;" more owners not shown","")</f>
+        <v/>
+      </c>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+    </row>
+    <row r="34" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="33">
         <f ca="1">IF(Lists!$M6="","",INT(Lists!$L6))</f>
         <v>46299</v>
       </c>
-      <c r="I14" s="9" t="str">
+      <c r="C34" s="6" t="str">
         <f ca="1">IF(Lists!$M6="","",INDEX(Tasks[Task],Lists!$M6)&amp;"")</f>
         <v>Quote follow-up calls</v>
       </c>
-      <c r="J14" s="9" t="str">
+      <c r="D34" s="37">
+        <f ca="1">IF(Lists!$M6="","",INT(Lists!$L6)-TODAY())</f>
+        <v>2</v>
+      </c>
+      <c r="E34" s="6" t="str">
         <f ca="1">IF(Lists!$M6="","",INDEX(Tasks[Owner],Lists!$M6)&amp;"")</f>
         <v>Casey L.</v>
       </c>
-      <c r="K14" s="9" t="str">
+      <c r="F34" s="6" t="str">
         <f ca="1">IF(Lists!$M6="","",INDEX(Tasks[Status],Lists!$M6)&amp;"")</f>
         <v>Not started</v>
       </c>
-      <c r="L14" s="9" t="str">
+      <c r="G34" s="6" t="str">
         <f ca="1">IF(Lists!$M6="","",INDEX(Tasks[Priority],Lists!$M6)&amp;"")</f>
         <v>High</v>
       </c>
-      <c r="M14" s="53">
+      <c r="H34" s="8">
         <f ca="1">IF(Lists!$M6="","",INDEX(Tasks[% Complete],Lists!$M6))</f>
         <v>0</v>
       </c>
-      <c r="N14" s="54">
-        <f ca="1">IF(Lists!$M6="","",INT(Lists!$L6)-TODAY())</f>
-        <v>2</v>
-      </c>
-      <c r="O14" s="9" t="str">
+      <c r="I34" s="6">
+        <f ca="1">IF(H34="","",H34)</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="str">
         <f ca="1">IF(Lists!$M6="","",INDEX(Tasks[Department],Lists!$M6)&amp;"")</f>
         <v>Sales</v>
       </c>
-      <c r="P14" s="9"/>
-    </row>
-    <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="50">
-        <f ca="1">IF(Lists!$I7="","",INT(Lists!$H7))</f>
-        <v>46300</v>
-      </c>
-      <c r="C15" s="39" t="str">
-        <f ca="1">IF(Lists!$I7="","",INDEX(Tasks[Task],Lists!$I7)&amp;"")</f>
-        <v>Laptop refresh order</v>
-      </c>
-      <c r="D15" s="39" t="str">
-        <f ca="1">IF(Lists!$I7="","",INDEX(Tasks[Owner],Lists!$I7)&amp;"")</f>
-        <v>Riley P.</v>
-      </c>
-      <c r="E15" s="39" t="str">
-        <f ca="1">IF(Lists!$I7="","",INDEX(Tasks[Priority],Lists!$I7)&amp;"")</f>
-        <v>Medium</v>
-      </c>
-      <c r="F15" s="52">
-        <f ca="1">IF(Lists!$I7="","",INDEX(Tasks[% Complete],Lists!$I7))</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="51">
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+    </row>
+    <row r="35" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="33">
         <f ca="1">IF(Lists!$M7="","",INT(Lists!$L7))</f>
         <v>46300</v>
       </c>
-      <c r="I15" s="9" t="str">
+      <c r="C35" s="6" t="str">
         <f ca="1">IF(Lists!$M7="","",INDEX(Tasks[Task],Lists!$M7)&amp;"")</f>
         <v>Laptop refresh order</v>
       </c>
-      <c r="J15" s="9" t="str">
+      <c r="D35" s="37">
+        <f ca="1">IF(Lists!$M7="","",INT(Lists!$L7)-TODAY())</f>
+        <v>3</v>
+      </c>
+      <c r="E35" s="6" t="str">
         <f ca="1">IF(Lists!$M7="","",INDEX(Tasks[Owner],Lists!$M7)&amp;"")</f>
         <v>Riley P.</v>
       </c>
-      <c r="K15" s="9" t="str">
+      <c r="F35" s="6" t="str">
         <f ca="1">IF(Lists!$M7="","",INDEX(Tasks[Status],Lists!$M7)&amp;"")</f>
         <v>In progress</v>
       </c>
-      <c r="L15" s="9" t="str">
+      <c r="G35" s="6" t="str">
         <f ca="1">IF(Lists!$M7="","",INDEX(Tasks[Priority],Lists!$M7)&amp;"")</f>
         <v>Medium</v>
       </c>
-      <c r="M15" s="53">
+      <c r="H35" s="8">
         <f ca="1">IF(Lists!$M7="","",INDEX(Tasks[% Complete],Lists!$M7))</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="N15" s="54">
-        <f ca="1">IF(Lists!$M7="","",INT(Lists!$L7)-TODAY())</f>
-        <v>3</v>
-      </c>
-      <c r="O15" s="9" t="str">
+      <c r="I35" s="6">
+        <f ca="1">IF(H35="","",H35)</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J35" s="6" t="str">
         <f ca="1">IF(Lists!$M7="","",INDEX(Tasks[Department],Lists!$M7)&amp;"")</f>
         <v>IT</v>
       </c>
-      <c r="P15" s="9"/>
-    </row>
-    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="50">
-        <f ca="1">IF(Lists!$I8="","",INT(Lists!$H8))</f>
-        <v>46302</v>
-      </c>
-      <c r="C16" s="39" t="str">
-        <f ca="1">IF(Lists!$I8="","",INDEX(Tasks[Task],Lists!$I8)&amp;"")</f>
-        <v>Benefits enrollment memo</v>
-      </c>
-      <c r="D16" s="39" t="str">
-        <f ca="1">IF(Lists!$I8="","",INDEX(Tasks[Owner],Lists!$I8)&amp;"")</f>
-        <v>Morgan T.</v>
-      </c>
-      <c r="E16" s="39" t="str">
-        <f ca="1">IF(Lists!$I8="","",INDEX(Tasks[Priority],Lists!$I8)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="F16" s="52">
-        <f ca="1">IF(Lists!$I8="","",INDEX(Tasks[% Complete],Lists!$I8))</f>
-        <v>0.35</v>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="51">
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+    </row>
+    <row r="36" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="6"/>
+      <c r="B36" s="33">
         <f ca="1">IF(Lists!$M8="","",INT(Lists!$L8))</f>
         <v>46302</v>
       </c>
-      <c r="I16" s="9" t="str">
+      <c r="C36" s="6" t="str">
         <f ca="1">IF(Lists!$M8="","",INDEX(Tasks[Task],Lists!$M8)&amp;"")</f>
         <v>Benefits enrollment memo</v>
       </c>
-      <c r="J16" s="9" t="str">
+      <c r="D36" s="37">
+        <f ca="1">IF(Lists!$M8="","",INT(Lists!$L8)-TODAY())</f>
+        <v>5</v>
+      </c>
+      <c r="E36" s="6" t="str">
         <f ca="1">IF(Lists!$M8="","",INDEX(Tasks[Owner],Lists!$M8)&amp;"")</f>
         <v>Morgan T.</v>
       </c>
-      <c r="K16" s="9" t="str">
+      <c r="F36" s="6" t="str">
         <f ca="1">IF(Lists!$M8="","",INDEX(Tasks[Status],Lists!$M8)&amp;"")</f>
         <v>In progress</v>
       </c>
-      <c r="L16" s="9" t="str">
+      <c r="G36" s="6" t="str">
         <f ca="1">IF(Lists!$M8="","",INDEX(Tasks[Priority],Lists!$M8)&amp;"")</f>
         <v>High</v>
       </c>
-      <c r="M16" s="53">
+      <c r="H36" s="8">
         <f ca="1">IF(Lists!$M8="","",INDEX(Tasks[% Complete],Lists!$M8))</f>
         <v>0.35</v>
       </c>
-      <c r="N16" s="54">
-        <f ca="1">IF(Lists!$M8="","",INT(Lists!$L8)-TODAY())</f>
-        <v>5</v>
-      </c>
-      <c r="O16" s="9" t="str">
+      <c r="I36" s="6">
+        <f ca="1">IF(H36="","",H36)</f>
+        <v>0.35</v>
+      </c>
+      <c r="J36" s="6" t="str">
         <f ca="1">IF(Lists!$M8="","",INDEX(Tasks[Department],Lists!$M8)&amp;"")</f>
         <v>HR</v>
       </c>
-      <c r="P16" s="9"/>
-    </row>
-    <row r="17" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="50">
-        <f ca="1">IF(Lists!$I9="","",INT(Lists!$H9))</f>
-        <v>46303</v>
-      </c>
-      <c r="C17" s="39" t="str">
-        <f ca="1">IF(Lists!$I9="","",INDEX(Tasks[Task],Lists!$I9)&amp;"")</f>
-        <v>Fleet insurance renewal</v>
-      </c>
-      <c r="D17" s="39" t="str">
-        <f ca="1">IF(Lists!$I9="","",INDEX(Tasks[Owner],Lists!$I9)&amp;"")</f>
-        <v>Taylor R.</v>
-      </c>
-      <c r="E17" s="39" t="str">
-        <f ca="1">IF(Lists!$I9="","",INDEX(Tasks[Priority],Lists!$I9)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="F17" s="52">
-        <f ca="1">IF(Lists!$I9="","",INDEX(Tasks[% Complete],Lists!$I9))</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="16" t="str">
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+    </row>
+    <row r="37" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="6"/>
+      <c r="B37" s="21" t="str">
         <f ca="1">IF(SUMPRODUCT(CondUpcoming)&gt;5,"+ "&amp;(SUMPRODUCT(CondUpcoming)-5)&amp;" more not shown","")</f>
         <v>+ 21 more not shown</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-    </row>
-    <row r="18" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="50" t="str">
-        <f ca="1">IF(Lists!$I10="","",INT(Lists!$H10))</f>
-        <v/>
-      </c>
-      <c r="C18" s="39" t="str">
-        <f ca="1">IF(Lists!$I10="","",INDEX(Tasks[Task],Lists!$I10)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="39" t="str">
-        <f ca="1">IF(Lists!$I10="","",INDEX(Tasks[Owner],Lists!$I10)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="39" t="str">
-        <f ca="1">IF(Lists!$I10="","",INDEX(Tasks[Priority],Lists!$I10)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="52" t="str">
-        <f ca="1">IF(Lists!$I10="","",INDEX(Tasks[% Complete],Lists!$I10))</f>
-        <v/>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-    </row>
-    <row r="19" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="50" t="str">
-        <f ca="1">IF(Lists!$I11="","",INT(Lists!$H11))</f>
-        <v/>
-      </c>
-      <c r="C19" s="39" t="str">
-        <f ca="1">IF(Lists!$I11="","",INDEX(Tasks[Task],Lists!$I11)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="39" t="str">
-        <f ca="1">IF(Lists!$I11="","",INDEX(Tasks[Owner],Lists!$I11)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="39" t="str">
-        <f ca="1">IF(Lists!$I11="","",INDEX(Tasks[Priority],Lists!$I11)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="52" t="str">
-        <f ca="1">IF(Lists!$I11="","",INDEX(Tasks[% Complete],Lists!$I11))</f>
-        <v/>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="16" t="str">
-        <f>"Open tasks first, then by due date   |   "&amp;KpiTotal&amp;" match the filters"</f>
-        <v>Open tasks first, then by due date   |   42 match the filters</v>
-      </c>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-    </row>
-    <row r="20" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="43" t="str">
-        <f ca="1">IF(KpiDueThisWeek&gt;8,"+ "&amp;(KpiDueThisWeek-8)&amp;" more not shown","")</f>
-        <v/>
-      </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="K20" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="N20" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="O20" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="9"/>
-    </row>
-    <row r="21" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="51">
-        <f>IF(Lists!$Q4="","",IF(MOD(INT(Lists!$P4),100000)=99999,"",MOD(INT(Lists!$P4),100000)))</f>
-        <v>46282</v>
-      </c>
-      <c r="I21" s="9" t="str">
-        <f>IF(Lists!$Q4="","No tasks match these filters",INDEX(Tasks[Task],Lists!$Q4)&amp;"")</f>
-        <v>Trade show booth order</v>
-      </c>
-      <c r="J21" s="9" t="str">
-        <f>IF(Lists!$Q4="","",INDEX(Tasks[Owner],Lists!$Q4)&amp;"")</f>
-        <v>Casey L.</v>
-      </c>
-      <c r="K21" s="9" t="str">
-        <f>IF(Lists!$Q4="","",INDEX(Tasks[Status],Lists!$Q4)&amp;"")</f>
-        <v>Blocked</v>
-      </c>
-      <c r="L21" s="9" t="str">
-        <f>IF(Lists!$Q4="","",INDEX(Tasks[Priority],Lists!$Q4)&amp;"")</f>
-        <v>Medium</v>
-      </c>
-      <c r="M21" s="53">
-        <f>IF(Lists!$Q4="","",INDEX(Tasks[% Complete],Lists!$Q4))</f>
-        <v>0.3</v>
-      </c>
-      <c r="N21" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q4="",H21="",K21="Done"),"",IF(H21&lt;TODAY(),"OVERDUE",IF(H21&lt;=TODAY()+6,"This week","")))</f>
-        <v>OVERDUE</v>
-      </c>
-      <c r="O21" s="9" t="str">
-        <f>IF(Lists!$Q4="","",INDEX(Tasks[Department],Lists!$Q4)&amp;"")</f>
-        <v>Sales</v>
-      </c>
-      <c r="P21" s="9"/>
-    </row>
-    <row r="22" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="51">
-        <f>IF(Lists!$Q5="","",IF(MOD(INT(Lists!$P5),100000)=99999,"",MOD(INT(Lists!$P5),100000)))</f>
-        <v>46285</v>
-      </c>
-      <c r="I22" s="9" t="str">
-        <f>IF(Lists!$Q5="","",INDEX(Tasks[Task],Lists!$Q5)&amp;"")</f>
-        <v>Vendor contract renewal</v>
-      </c>
-      <c r="J22" s="9" t="str">
-        <f>IF(Lists!$Q5="","",INDEX(Tasks[Owner],Lists!$Q5)&amp;"")</f>
-        <v>Taylor R.</v>
-      </c>
-      <c r="K22" s="9" t="str">
-        <f>IF(Lists!$Q5="","",INDEX(Tasks[Status],Lists!$Q5)&amp;"")</f>
-        <v>In progress</v>
-      </c>
-      <c r="L22" s="9" t="str">
-        <f>IF(Lists!$Q5="","",INDEX(Tasks[Priority],Lists!$Q5)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="M22" s="53">
-        <f>IF(Lists!$Q5="","",INDEX(Tasks[% Complete],Lists!$Q5))</f>
-        <v>0.7</v>
-      </c>
-      <c r="N22" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q5="",H22="",K22="Done"),"",IF(H22&lt;TODAY(),"OVERDUE",IF(H22&lt;=TODAY()+6,"This week","")))</f>
-        <v>OVERDUE</v>
-      </c>
-      <c r="O22" s="9" t="str">
-        <f>IF(Lists!$Q5="","",INDEX(Tasks[Department],Lists!$Q5)&amp;"")</f>
-        <v>Operations</v>
-      </c>
-      <c r="P22" s="9"/>
-    </row>
-    <row r="23" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
-      <c r="B23" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="D23" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="E23" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="56" t="s">
-        <v>151</v>
-      </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="51">
-        <f>IF(Lists!$Q6="","",IF(MOD(INT(Lists!$P6),100000)=99999,"",MOD(INT(Lists!$P6),100000)))</f>
-        <v>46289</v>
-      </c>
-      <c r="I23" s="9" t="str">
-        <f>IF(Lists!$Q6="","",INDEX(Tasks[Task],Lists!$Q6)&amp;"")</f>
-        <v>Customer survey mailing</v>
-      </c>
-      <c r="J23" s="9" t="str">
-        <f>IF(Lists!$Q6="","",INDEX(Tasks[Owner],Lists!$Q6)&amp;"")</f>
-        <v>Casey L.</v>
-      </c>
-      <c r="K23" s="9" t="str">
-        <f>IF(Lists!$Q6="","",INDEX(Tasks[Status],Lists!$Q6)&amp;"")</f>
-        <v>In progress</v>
-      </c>
-      <c r="L23" s="9" t="str">
-        <f>IF(Lists!$Q6="","",INDEX(Tasks[Priority],Lists!$Q6)&amp;"")</f>
-        <v>Medium</v>
-      </c>
-      <c r="M23" s="53">
-        <f>IF(Lists!$Q6="","",INDEX(Tasks[% Complete],Lists!$Q6))</f>
-        <v>0.6</v>
-      </c>
-      <c r="N23" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q6="",H23="",K23="Done"),"",IF(H23&lt;TODAY(),"OVERDUE",IF(H23&lt;=TODAY()+6,"This week","")))</f>
-        <v>OVERDUE</v>
-      </c>
-      <c r="O23" s="9" t="str">
-        <f>IF(Lists!$Q6="","",INDEX(Tasks[Department],Lists!$Q6)&amp;"")</f>
-        <v>Sales</v>
-      </c>
-      <c r="P23" s="9"/>
-    </row>
-    <row r="24" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9" t="str">
-        <f>IF(Lists!$A5="","",Lists!$A5)</f>
-        <v>Avery K.</v>
-      </c>
-      <c r="C24" s="53">
-        <f>IF(OR(B24="",D24=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=B24)*Tasks[% Complete])/D24)</f>
-        <v>0.31</v>
-      </c>
-      <c r="D24" s="55">
-        <f>IF(B24="","",SUMPRODUCT(InScope*(Tasks[Owner]=B24)))</f>
-        <v>5</v>
-      </c>
-      <c r="E24" s="55">
-        <f>IF(B24="","",SUMPRODUCT(InScope*(Tasks[Owner]=B24)*(Tasks[Status]="Done")))</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="55">
-        <f ca="1">IF(B24="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=B24)))</f>
-        <v>1</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="51">
-        <f>IF(Lists!$Q7="","",IF(MOD(INT(Lists!$P7),100000)=99999,"",MOD(INT(Lists!$P7),100000)))</f>
-        <v>46291</v>
-      </c>
-      <c r="I24" s="9" t="str">
-        <f>IF(Lists!$Q7="","",INDEX(Tasks[Task],Lists!$Q7)&amp;"")</f>
-        <v>Backup system test</v>
-      </c>
-      <c r="J24" s="9" t="str">
-        <f>IF(Lists!$Q7="","",INDEX(Tasks[Owner],Lists!$Q7)&amp;"")</f>
-        <v>Riley P.</v>
-      </c>
-      <c r="K24" s="9" t="str">
-        <f>IF(Lists!$Q7="","",INDEX(Tasks[Status],Lists!$Q7)&amp;"")</f>
-        <v>Blocked</v>
-      </c>
-      <c r="L24" s="9" t="str">
-        <f>IF(Lists!$Q7="","",INDEX(Tasks[Priority],Lists!$Q7)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="M24" s="53">
-        <f>IF(Lists!$Q7="","",INDEX(Tasks[% Complete],Lists!$Q7))</f>
-        <v>0.4</v>
-      </c>
-      <c r="N24" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q7="",H24="",K24="Done"),"",IF(H24&lt;TODAY(),"OVERDUE",IF(H24&lt;=TODAY()+6,"This week","")))</f>
-        <v>OVERDUE</v>
-      </c>
-      <c r="O24" s="9" t="str">
-        <f>IF(Lists!$Q7="","",INDEX(Tasks[Department],Lists!$Q7)&amp;"")</f>
-        <v>IT</v>
-      </c>
-      <c r="P24" s="9"/>
-    </row>
-    <row r="25" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9" t="str">
-        <f>IF(Lists!$A6="","",Lists!$A6)</f>
-        <v>Casey L.</v>
-      </c>
-      <c r="C25" s="53">
-        <f>IF(OR(B25="",D25=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=B25)*Tasks[% Complete])/D25)</f>
-        <v>0.37777777777777782</v>
-      </c>
-      <c r="D25" s="55">
-        <f>IF(B25="","",SUMPRODUCT(InScope*(Tasks[Owner]=B25)))</f>
-        <v>9</v>
-      </c>
-      <c r="E25" s="55">
-        <f>IF(B25="","",SUMPRODUCT(InScope*(Tasks[Owner]=B25)*(Tasks[Status]="Done")))</f>
-        <v>2</v>
-      </c>
-      <c r="F25" s="55">
-        <f ca="1">IF(B25="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=B25)))</f>
-        <v>2</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="51">
-        <f>IF(Lists!$Q8="","",IF(MOD(INT(Lists!$P8),100000)=99999,"",MOD(INT(Lists!$P8),100000)))</f>
-        <v>46293</v>
-      </c>
-      <c r="I25" s="9" t="str">
-        <f>IF(Lists!$Q8="","",INDEX(Tasks[Task],Lists!$Q8)&amp;"")</f>
-        <v>Expense policy update</v>
-      </c>
-      <c r="J25" s="9" t="str">
-        <f>IF(Lists!$Q8="","",INDEX(Tasks[Owner],Lists!$Q8)&amp;"")</f>
-        <v>Jordan M.</v>
-      </c>
-      <c r="K25" s="9" t="str">
-        <f>IF(Lists!$Q8="","",INDEX(Tasks[Status],Lists!$Q8)&amp;"")</f>
-        <v>In progress</v>
-      </c>
-      <c r="L25" s="9" t="str">
-        <f>IF(Lists!$Q8="","",INDEX(Tasks[Priority],Lists!$Q8)&amp;"")</f>
-        <v>Medium</v>
-      </c>
-      <c r="M25" s="53">
-        <f>IF(Lists!$Q8="","",INDEX(Tasks[% Complete],Lists!$Q8))</f>
-        <v>0.8</v>
-      </c>
-      <c r="N25" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q8="",H25="",K25="Done"),"",IF(H25&lt;TODAY(),"OVERDUE",IF(H25&lt;=TODAY()+6,"This week","")))</f>
-        <v>OVERDUE</v>
-      </c>
-      <c r="O25" s="9" t="str">
-        <f>IF(Lists!$Q8="","",INDEX(Tasks[Department],Lists!$Q8)&amp;"")</f>
-        <v>Finance</v>
-      </c>
-      <c r="P25" s="9"/>
-    </row>
-    <row r="26" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9" t="str">
-        <f>IF(Lists!$A7="","",Lists!$A7)</f>
-        <v>Jordan M.</v>
-      </c>
-      <c r="C26" s="53">
-        <f>IF(OR(B26="",D26=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=B26)*Tasks[% Complete])/D26)</f>
-        <v>0.51875000000000004</v>
-      </c>
-      <c r="D26" s="55">
-        <f>IF(B26="","",SUMPRODUCT(InScope*(Tasks[Owner]=B26)))</f>
-        <v>8</v>
-      </c>
-      <c r="E26" s="55">
-        <f>IF(B26="","",SUMPRODUCT(InScope*(Tasks[Owner]=B26)*(Tasks[Status]="Done")))</f>
-        <v>2</v>
-      </c>
-      <c r="F26" s="55">
-        <f ca="1">IF(B26="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=B26)))</f>
-        <v>1</v>
-      </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="51">
-        <f>IF(Lists!$Q9="","",IF(MOD(INT(Lists!$P9),100000)=99999,"",MOD(INT(Lists!$P9),100000)))</f>
-        <v>46295</v>
-      </c>
-      <c r="I26" s="9" t="str">
-        <f>IF(Lists!$Q9="","",INDEX(Tasks[Task],Lists!$Q9)&amp;"")</f>
-        <v>Safety training sign-off</v>
-      </c>
-      <c r="J26" s="9" t="str">
-        <f>IF(Lists!$Q9="","",INDEX(Tasks[Owner],Lists!$Q9)&amp;"")</f>
-        <v>Morgan T.</v>
-      </c>
-      <c r="K26" s="9" t="str">
-        <f>IF(Lists!$Q9="","",INDEX(Tasks[Status],Lists!$Q9)&amp;"")</f>
-        <v>Not started</v>
-      </c>
-      <c r="L26" s="9" t="str">
-        <f>IF(Lists!$Q9="","",INDEX(Tasks[Priority],Lists!$Q9)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="M26" s="53">
-        <f>IF(Lists!$Q9="","",INDEX(Tasks[% Complete],Lists!$Q9))</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q9="",H26="",K26="Done"),"",IF(H26&lt;TODAY(),"OVERDUE",IF(H26&lt;=TODAY()+6,"This week","")))</f>
-        <v>OVERDUE</v>
-      </c>
-      <c r="O26" s="9" t="str">
-        <f>IF(Lists!$Q9="","",INDEX(Tasks[Department],Lists!$Q9)&amp;"")</f>
-        <v>HR</v>
-      </c>
-      <c r="P26" s="9"/>
-    </row>
-    <row r="27" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9" t="str">
-        <f>IF(Lists!$A8="","",Lists!$A8)</f>
-        <v>Morgan T.</v>
-      </c>
-      <c r="C27" s="53">
-        <f>IF(OR(B27="",D27=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=B27)*Tasks[% Complete])/D27)</f>
-        <v>0.35714285714285715</v>
-      </c>
-      <c r="D27" s="55">
-        <f>IF(B27="","",SUMPRODUCT(InScope*(Tasks[Owner]=B27)))</f>
-        <v>7</v>
-      </c>
-      <c r="E27" s="55">
-        <f>IF(B27="","",SUMPRODUCT(InScope*(Tasks[Owner]=B27)*(Tasks[Status]="Done")))</f>
-        <v>2</v>
-      </c>
-      <c r="F27" s="55">
-        <f ca="1">IF(B27="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=B27)))</f>
-        <v>1</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="51">
-        <f>IF(Lists!$Q10="","",IF(MOD(INT(Lists!$P10),100000)=99999,"",MOD(INT(Lists!$P10),100000)))</f>
-        <v>46296</v>
-      </c>
-      <c r="I27" s="9" t="str">
-        <f>IF(Lists!$Q10="","",INDEX(Tasks[Task],Lists!$Q10)&amp;"")</f>
-        <v>Forklift inspection</v>
-      </c>
-      <c r="J27" s="9" t="str">
-        <f>IF(Lists!$Q10="","",INDEX(Tasks[Owner],Lists!$Q10)&amp;"")</f>
-        <v>Avery K.</v>
-      </c>
-      <c r="K27" s="9" t="str">
-        <f>IF(Lists!$Q10="","",INDEX(Tasks[Status],Lists!$Q10)&amp;"")</f>
-        <v>In progress</v>
-      </c>
-      <c r="L27" s="9" t="str">
-        <f>IF(Lists!$Q10="","",INDEX(Tasks[Priority],Lists!$Q10)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="M27" s="53">
-        <f>IF(Lists!$Q10="","",INDEX(Tasks[% Complete],Lists!$Q10))</f>
-        <v>0.5</v>
-      </c>
-      <c r="N27" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q10="",H27="",K27="Done"),"",IF(H27&lt;TODAY(),"OVERDUE",IF(H27&lt;=TODAY()+6,"This week","")))</f>
-        <v>OVERDUE</v>
-      </c>
-      <c r="O27" s="9" t="str">
-        <f>IF(Lists!$Q10="","",INDEX(Tasks[Department],Lists!$Q10)&amp;"")</f>
-        <v>Operations</v>
-      </c>
-      <c r="P27" s="9"/>
-    </row>
-    <row r="28" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9" t="str">
-        <f>IF(Lists!$A9="","",Lists!$A9)</f>
-        <v>Riley P.</v>
-      </c>
-      <c r="C28" s="53">
-        <f>IF(OR(B28="",D28=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=B28)*Tasks[% Complete])/D28)</f>
-        <v>0.41875000000000001</v>
-      </c>
-      <c r="D28" s="55">
-        <f>IF(B28="","",SUMPRODUCT(InScope*(Tasks[Owner]=B28)))</f>
-        <v>8</v>
-      </c>
-      <c r="E28" s="55">
-        <f>IF(B28="","",SUMPRODUCT(InScope*(Tasks[Owner]=B28)*(Tasks[Status]="Done")))</f>
-        <v>2</v>
-      </c>
-      <c r="F28" s="55">
-        <f ca="1">IF(B28="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=B28)))</f>
-        <v>1</v>
-      </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="51">
-        <f>IF(Lists!$Q11="","",IF(MOD(INT(Lists!$P11),100000)=99999,"",MOD(INT(Lists!$P11),100000)))</f>
-        <v>46297</v>
-      </c>
-      <c r="I28" s="9" t="str">
-        <f>IF(Lists!$Q11="","",INDEX(Tasks[Task],Lists!$Q11)&amp;"")</f>
-        <v>Payroll calendar 2027</v>
-      </c>
-      <c r="J28" s="9" t="str">
-        <f>IF(Lists!$Q11="","",INDEX(Tasks[Owner],Lists!$Q11)&amp;"")</f>
-        <v>Jordan M.</v>
-      </c>
-      <c r="K28" s="9" t="str">
-        <f>IF(Lists!$Q11="","",INDEX(Tasks[Status],Lists!$Q11)&amp;"")</f>
-        <v>In progress</v>
-      </c>
-      <c r="L28" s="9" t="str">
-        <f>IF(Lists!$Q11="","",INDEX(Tasks[Priority],Lists!$Q11)&amp;"")</f>
-        <v>Medium</v>
-      </c>
-      <c r="M28" s="53">
-        <f>IF(Lists!$Q11="","",INDEX(Tasks[% Complete],Lists!$Q11))</f>
-        <v>0.9</v>
-      </c>
-      <c r="N28" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q11="",H28="",K28="Done"),"",IF(H28&lt;TODAY(),"OVERDUE",IF(H28&lt;=TODAY()+6,"This week","")))</f>
-        <v>This week</v>
-      </c>
-      <c r="O28" s="9" t="str">
-        <f>IF(Lists!$Q11="","",INDEX(Tasks[Department],Lists!$Q11)&amp;"")</f>
-        <v>Finance</v>
-      </c>
-      <c r="P28" s="9"/>
-    </row>
-    <row r="29" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9" t="str">
-        <f>IF(Lists!$A10="","",Lists!$A10)</f>
-        <v>Taylor R.</v>
-      </c>
-      <c r="C29" s="53">
-        <f>IF(OR(B29="",D29=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=B29)*Tasks[% Complete])/D29)</f>
-        <v>0.42000000000000004</v>
-      </c>
-      <c r="D29" s="55">
-        <f>IF(B29="","",SUMPRODUCT(InScope*(Tasks[Owner]=B29)))</f>
-        <v>5</v>
-      </c>
-      <c r="E29" s="55">
-        <f>IF(B29="","",SUMPRODUCT(InScope*(Tasks[Owner]=B29)*(Tasks[Status]="Done")))</f>
-        <v>1</v>
-      </c>
-      <c r="F29" s="55">
-        <f ca="1">IF(B29="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=B29)))</f>
-        <v>1</v>
-      </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="51">
-        <f>IF(Lists!$Q12="","",IF(MOD(INT(Lists!$P12),100000)=99999,"",MOD(INT(Lists!$P12),100000)))</f>
-        <v>46298</v>
-      </c>
-      <c r="I29" s="9" t="str">
-        <f>IF(Lists!$Q12="","",INDEX(Tasks[Task],Lists!$Q12)&amp;"")</f>
-        <v>Warehouse rack labels</v>
-      </c>
-      <c r="J29" s="9" t="str">
-        <f>IF(Lists!$Q12="","",INDEX(Tasks[Owner],Lists!$Q12)&amp;"")</f>
-        <v>Avery K.</v>
-      </c>
-      <c r="K29" s="9" t="str">
-        <f>IF(Lists!$Q12="","",INDEX(Tasks[Status],Lists!$Q12)&amp;"")</f>
-        <v>In progress</v>
-      </c>
-      <c r="L29" s="9" t="str">
-        <f>IF(Lists!$Q12="","",INDEX(Tasks[Priority],Lists!$Q12)&amp;"")</f>
-        <v>Low</v>
-      </c>
-      <c r="M29" s="53">
-        <f>IF(Lists!$Q12="","",INDEX(Tasks[% Complete],Lists!$Q12))</f>
-        <v>0.75</v>
-      </c>
-      <c r="N29" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q12="",H29="",K29="Done"),"",IF(H29&lt;TODAY(),"OVERDUE",IF(H29&lt;=TODAY()+6,"This week","")))</f>
-        <v>This week</v>
-      </c>
-      <c r="O29" s="9" t="str">
-        <f>IF(Lists!$Q12="","",INDEX(Tasks[Department],Lists!$Q12)&amp;"")</f>
-        <v>Operations</v>
-      </c>
-      <c r="P29" s="9"/>
-    </row>
-    <row r="30" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9" t="str">
-        <f>IF(Lists!$A11="","",Lists!$A11)</f>
-        <v/>
-      </c>
-      <c r="C30" s="53" t="str">
-        <f>IF(OR(B30="",D30=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=B30)*Tasks[% Complete])/D30)</f>
-        <v/>
-      </c>
-      <c r="D30" s="55" t="str">
-        <f>IF(B30="","",SUMPRODUCT(InScope*(Tasks[Owner]=B30)))</f>
-        <v/>
-      </c>
-      <c r="E30" s="55" t="str">
-        <f>IF(B30="","",SUMPRODUCT(InScope*(Tasks[Owner]=B30)*(Tasks[Status]="Done")))</f>
-        <v/>
-      </c>
-      <c r="F30" s="55" t="str">
-        <f>IF(B30="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=B30)))</f>
-        <v/>
-      </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="51">
-        <f>IF(Lists!$Q13="","",IF(MOD(INT(Lists!$P13),100000)=99999,"",MOD(INT(Lists!$P13),100000)))</f>
-        <v>46299</v>
-      </c>
-      <c r="I30" s="9" t="str">
-        <f>IF(Lists!$Q13="","",INDEX(Tasks[Task],Lists!$Q13)&amp;"")</f>
-        <v>Quote follow-up calls</v>
-      </c>
-      <c r="J30" s="9" t="str">
-        <f>IF(Lists!$Q13="","",INDEX(Tasks[Owner],Lists!$Q13)&amp;"")</f>
-        <v>Casey L.</v>
-      </c>
-      <c r="K30" s="9" t="str">
-        <f>IF(Lists!$Q13="","",INDEX(Tasks[Status],Lists!$Q13)&amp;"")</f>
-        <v>Not started</v>
-      </c>
-      <c r="L30" s="9" t="str">
-        <f>IF(Lists!$Q13="","",INDEX(Tasks[Priority],Lists!$Q13)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="M30" s="53">
-        <f>IF(Lists!$Q13="","",INDEX(Tasks[% Complete],Lists!$Q13))</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q13="",H30="",K30="Done"),"",IF(H30&lt;TODAY(),"OVERDUE",IF(H30&lt;=TODAY()+6,"This week","")))</f>
-        <v>This week</v>
-      </c>
-      <c r="O30" s="9" t="str">
-        <f>IF(Lists!$Q13="","",INDEX(Tasks[Department],Lists!$Q13)&amp;"")</f>
-        <v>Sales</v>
-      </c>
-      <c r="P30" s="9"/>
-    </row>
-    <row r="31" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9" t="str">
-        <f>IF(Lists!$A12="","",Lists!$A12)</f>
-        <v/>
-      </c>
-      <c r="C31" s="53" t="str">
-        <f>IF(OR(B31="",D31=0),"",SUMPRODUCT(InScope*(Tasks[Owner]=B31)*Tasks[% Complete])/D31)</f>
-        <v/>
-      </c>
-      <c r="D31" s="55" t="str">
-        <f>IF(B31="","",SUMPRODUCT(InScope*(Tasks[Owner]=B31)))</f>
-        <v/>
-      </c>
-      <c r="E31" s="55" t="str">
-        <f>IF(B31="","",SUMPRODUCT(InScope*(Tasks[Owner]=B31)*(Tasks[Status]="Done")))</f>
-        <v/>
-      </c>
-      <c r="F31" s="55" t="str">
-        <f>IF(B31="","",SUMPRODUCT(CondOverdue*(Tasks[Owner]=B31)))</f>
-        <v/>
-      </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="51">
-        <f>IF(Lists!$Q14="","",IF(MOD(INT(Lists!$P14),100000)=99999,"",MOD(INT(Lists!$P14),100000)))</f>
-        <v>46300</v>
-      </c>
-      <c r="I31" s="9" t="str">
-        <f>IF(Lists!$Q14="","",INDEX(Tasks[Task],Lists!$Q14)&amp;"")</f>
-        <v>Laptop refresh order</v>
-      </c>
-      <c r="J31" s="9" t="str">
-        <f>IF(Lists!$Q14="","",INDEX(Tasks[Owner],Lists!$Q14)&amp;"")</f>
-        <v>Riley P.</v>
-      </c>
-      <c r="K31" s="9" t="str">
-        <f>IF(Lists!$Q14="","",INDEX(Tasks[Status],Lists!$Q14)&amp;"")</f>
-        <v>In progress</v>
-      </c>
-      <c r="L31" s="9" t="str">
-        <f>IF(Lists!$Q14="","",INDEX(Tasks[Priority],Lists!$Q14)&amp;"")</f>
-        <v>Medium</v>
-      </c>
-      <c r="M31" s="53">
-        <f>IF(Lists!$Q14="","",INDEX(Tasks[% Complete],Lists!$Q14))</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="N31" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q14="",H31="",K31="Done"),"",IF(H31&lt;TODAY(),"OVERDUE",IF(H31&lt;=TODAY()+6,"This week","")))</f>
-        <v>This week</v>
-      </c>
-      <c r="O31" s="9" t="str">
-        <f>IF(Lists!$Q14="","",INDEX(Tasks[Department],Lists!$Q14)&amp;"")</f>
-        <v>IT</v>
-      </c>
-      <c r="P31" s="9"/>
-    </row>
-    <row r="32" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9"/>
-      <c r="B32" s="16" t="str">
-        <f>IF(COUNTIF(Lists!$A$5:$A$34,"?*")&gt;8,"+ "&amp;(COUNTIF(Lists!$A$5:$A$34,"?*")-8)&amp;" more owners not shown","")</f>
-        <v/>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="51">
-        <f>IF(Lists!$Q15="","",IF(MOD(INT(Lists!$P15),100000)=99999,"",MOD(INT(Lists!$P15),100000)))</f>
-        <v>46302</v>
-      </c>
-      <c r="I32" s="9" t="str">
-        <f>IF(Lists!$Q15="","",INDEX(Tasks[Task],Lists!$Q15)&amp;"")</f>
-        <v>Benefits enrollment memo</v>
-      </c>
-      <c r="J32" s="9" t="str">
-        <f>IF(Lists!$Q15="","",INDEX(Tasks[Owner],Lists!$Q15)&amp;"")</f>
-        <v>Morgan T.</v>
-      </c>
-      <c r="K32" s="9" t="str">
-        <f>IF(Lists!$Q15="","",INDEX(Tasks[Status],Lists!$Q15)&amp;"")</f>
-        <v>In progress</v>
-      </c>
-      <c r="L32" s="9" t="str">
-        <f>IF(Lists!$Q15="","",INDEX(Tasks[Priority],Lists!$Q15)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="M32" s="53">
-        <f>IF(Lists!$Q15="","",INDEX(Tasks[% Complete],Lists!$Q15))</f>
-        <v>0.35</v>
-      </c>
-      <c r="N32" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q15="",H32="",K32="Done"),"",IF(H32&lt;TODAY(),"OVERDUE",IF(H32&lt;=TODAY()+6,"This week","")))</f>
-        <v>This week</v>
-      </c>
-      <c r="O32" s="9" t="str">
-        <f>IF(Lists!$Q15="","",INDEX(Tasks[Department],Lists!$Q15)&amp;"")</f>
-        <v>HR</v>
-      </c>
-      <c r="P32" s="9"/>
-    </row>
-    <row r="33" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="51">
-        <f>IF(Lists!$Q16="","",IF(MOD(INT(Lists!$P16),100000)=99999,"",MOD(INT(Lists!$P16),100000)))</f>
-        <v>46303</v>
-      </c>
-      <c r="I33" s="9" t="str">
-        <f>IF(Lists!$Q16="","",INDEX(Tasks[Task],Lists!$Q16)&amp;"")</f>
-        <v>Fleet insurance renewal</v>
-      </c>
-      <c r="J33" s="9" t="str">
-        <f>IF(Lists!$Q16="","",INDEX(Tasks[Owner],Lists!$Q16)&amp;"")</f>
-        <v>Taylor R.</v>
-      </c>
-      <c r="K33" s="9" t="str">
-        <f>IF(Lists!$Q16="","",INDEX(Tasks[Status],Lists!$Q16)&amp;"")</f>
-        <v>Not started</v>
-      </c>
-      <c r="L33" s="9" t="str">
-        <f>IF(Lists!$Q16="","",INDEX(Tasks[Priority],Lists!$Q16)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="M33" s="53">
-        <f>IF(Lists!$Q16="","",INDEX(Tasks[% Complete],Lists!$Q16))</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q16="",H33="",K33="Done"),"",IF(H33&lt;TODAY(),"OVERDUE",IF(H33&lt;=TODAY()+6,"This week","")))</f>
-        <v>This week</v>
-      </c>
-      <c r="O33" s="9" t="str">
-        <f>IF(Lists!$Q16="","",INDEX(Tasks[Department],Lists!$Q16)&amp;"")</f>
-        <v>Operations</v>
-      </c>
-      <c r="P33" s="9"/>
-    </row>
-    <row r="34" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="51">
-        <f>IF(Lists!$Q17="","",IF(MOD(INT(Lists!$P17),100000)=99999,"",MOD(INT(Lists!$P17),100000)))</f>
-        <v>46304</v>
-      </c>
-      <c r="I34" s="9" t="str">
-        <f>IF(Lists!$Q17="","",INDEX(Tasks[Task],Lists!$Q17)&amp;"")</f>
-        <v>Budget draft for 2027</v>
-      </c>
-      <c r="J34" s="9" t="str">
-        <f>IF(Lists!$Q17="","",INDEX(Tasks[Owner],Lists!$Q17)&amp;"")</f>
-        <v>Jordan M.</v>
-      </c>
-      <c r="K34" s="9" t="str">
-        <f>IF(Lists!$Q17="","",INDEX(Tasks[Status],Lists!$Q17)&amp;"")</f>
-        <v>In progress</v>
-      </c>
-      <c r="L34" s="9" t="str">
-        <f>IF(Lists!$Q17="","",INDEX(Tasks[Priority],Lists!$Q17)&amp;"")</f>
-        <v>High</v>
-      </c>
-      <c r="M34" s="53">
-        <f>IF(Lists!$Q17="","",INDEX(Tasks[% Complete],Lists!$Q17))</f>
-        <v>0.45</v>
-      </c>
-      <c r="N34" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q17="",H34="",K34="Done"),"",IF(H34&lt;TODAY(),"OVERDUE",IF(H34&lt;=TODAY()+6,"This week","")))</f>
-        <v/>
-      </c>
-      <c r="O34" s="9" t="str">
-        <f>IF(Lists!$Q17="","",INDEX(Tasks[Department],Lists!$Q17)&amp;"")</f>
-        <v>Finance</v>
-      </c>
-      <c r="P34" s="9"/>
-    </row>
-    <row r="35" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="51">
-        <f>IF(Lists!$Q18="","",IF(MOD(INT(Lists!$P18),100000)=99999,"",MOD(INT(Lists!$P18),100000)))</f>
-        <v>46305</v>
-      </c>
-      <c r="I35" s="9" t="str">
-        <f>IF(Lists!$Q18="","",INDEX(Tasks[Task],Lists!$Q18)&amp;"")</f>
-        <v>Website contact form fix</v>
-      </c>
-      <c r="J35" s="9" t="str">
-        <f>IF(Lists!$Q18="","",INDEX(Tasks[Owner],Lists!$Q18)&amp;"")</f>
-        <v>Riley P.</v>
-      </c>
-      <c r="K35" s="9" t="str">
-        <f>IF(Lists!$Q18="","",INDEX(Tasks[Status],Lists!$Q18)&amp;"")</f>
-        <v>Not started</v>
-      </c>
-      <c r="L35" s="9" t="str">
-        <f>IF(Lists!$Q18="","",INDEX(Tasks[Priority],Lists!$Q18)&amp;"")</f>
-        <v>Medium</v>
-      </c>
-      <c r="M35" s="53">
-        <f>IF(Lists!$Q18="","",INDEX(Tasks[% Complete],Lists!$Q18))</f>
-        <v>0</v>
-      </c>
-      <c r="N35" s="55" t="str">
-        <f ca="1">IF(OR(Lists!$Q18="",H35="",K35="Done"),"",IF(H35&lt;TODAY(),"OVERDUE",IF(H35&lt;=TODAY()+6,"This week","")))</f>
-        <v/>
-      </c>
-      <c r="O35" s="9" t="str">
-        <f>IF(Lists!$Q18="","",INDEX(Tasks[Department],Lists!$Q18)&amp;"")</f>
-        <v>IT</v>
-      </c>
-      <c r="P35" s="9"/>
-    </row>
-    <row r="36" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="16" t="str">
-        <f>IF(KpiTotal&gt;15,"+ "&amp;(KpiTotal-15)&amp;" more not shown","")</f>
-        <v>+ 27 more not shown</v>
-      </c>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-    </row>
-    <row r="37" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+    </row>
+    <row r="38" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6"/>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L8"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="M7:O8"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G8"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I8"/>
+  <mergeCells count="12">
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:M9"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="N8:Q9"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F9"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J9"/>
   </mergeCells>
-  <conditionalFormatting sqref="F12:F19">
+  <conditionalFormatting sqref="I13:I27">
     <cfRule type="dataBar" priority="1">
-      <dataBar>
+      <dataBar showValue="0">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="FFE8B84A"/>
+        <color rgb="FF0F766E"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88CA7355-8FBC-4163-B62E-73B131EF93AE}</x14:id>
+          <x14:id>{E35422CB-ABC0-43BF-B8A7-FC3FE7104BBB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M12:M16">
+  <conditionalFormatting sqref="I32:I36">
     <cfRule type="dataBar" priority="2">
-      <dataBar>
+      <dataBar showValue="0">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="FF7FB2E5"/>
+        <color rgb="FF0F766E"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9C0BAB09-3951-4C45-81C3-5E0E334A7CFA}</x14:id>
+          <x14:id>{25CF9E22-CE5E-445F-A44D-B79B8DAC43A1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M21:M35">
+  <conditionalFormatting sqref="Q13:Q20">
     <cfRule type="dataBar" priority="3">
-      <dataBar>
+      <dataBar showValue="0">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="FF7FB2E5"/>
+        <color rgb="FF0F766E"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E2A53AFF-9032-4773-981D-A77642FF4DB7}</x14:id>
+          <x14:id>{54681967-0840-4500-AD8C-E20FB4BA98A2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:C31">
+  <conditionalFormatting sqref="M25:M32">
     <cfRule type="dataBar" priority="4">
-      <dataBar>
+      <dataBar showValue="0">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="FF6DBE8B"/>
+        <color rgb="FF0F766E"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3F700B6D-9D8A-4367-B352-D75AC487BD9B}</x14:id>
+          <x14:id>{C3C1AD25-AE66-42ED-BA09-341FB0F71CDD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N21:N35">
+  <conditionalFormatting sqref="D13:D27">
     <cfRule type="cellIs" dxfId="9" priority="5" stopIfTrue="1" operator="equal">
       <formula>"OVERDUE"</formula>
     </cfRule>
@@ -3240,59 +3205,60 @@
       <formula>"This week"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E12:E19">
+  <conditionalFormatting sqref="F13:F27">
     <cfRule type="cellIs" dxfId="7" priority="7" stopIfTrue="1" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32:F36">
+    <cfRule type="cellIs" dxfId="5" priority="9" stopIfTrue="1" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="10" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13:G27">
+    <cfRule type="cellIs" dxfId="3" priority="11" stopIfTrue="1" operator="equal">
       <formula>"High"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L12:L16">
-    <cfRule type="cellIs" dxfId="6" priority="8" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="G32:G36">
+    <cfRule type="cellIs" dxfId="2" priority="12" stopIfTrue="1" operator="equal">
       <formula>"High"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L21:L35">
-    <cfRule type="cellIs" dxfId="5" priority="9" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="O13:O20">
+    <cfRule type="cellIs" dxfId="1" priority="13" stopIfTrue="1" operator="equal">
       <formula>"High"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K12:K16">
-    <cfRule type="cellIs" dxfId="4" priority="10" stopIfTrue="1" operator="equal">
-      <formula>"Blocked"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="11" stopIfTrue="1" operator="equal">
-      <formula>"Done"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K21:K35">
-    <cfRule type="cellIs" dxfId="2" priority="12" stopIfTrue="1" operator="equal">
-      <formula>"Blocked"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="13" stopIfTrue="1" operator="equal">
-      <formula>"Done"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F24:F31">
+  <conditionalFormatting sqref="Q25:Q32">
     <cfRule type="cellIs" dxfId="0" priority="14" stopIfTrue="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Owner" error="Pick a value from the list." sqref="C4" xr:uid="{62CBA168-226B-4D6C-BF81-143A340CD588}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Owner" error="Pick a value from the list." sqref="C5" xr:uid="{4B2C24AC-35A5-4D3C-832A-AD0FB8D99A49}">
       <formula1>OwnerList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Status" error="Pick a value from the list." sqref="E4" xr:uid="{F8CA078E-84BA-440E-A7D6-5726C085F552}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Status" error="Pick a value from the list." sqref="E5" xr:uid="{8C4DEA33-04EC-4DEB-8BB7-BFEE728A8E1B}">
       <formula1>StatusList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Year" error="Pick a value from the list." sqref="I4" xr:uid="{75B4F56E-14DF-4519-8A50-7C6E0BF0A07F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Year" error="Pick a value from the list." sqref="H5" xr:uid="{86F91568-DA26-4F57-BE09-E76E98A91480}">
       <formula1>YearList</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{88CA7355-8FBC-4163-B62E-73B131EF93AE}">
+          <x14:cfRule type="dataBar" id="{E35422CB-ABC0-43BF-B8A7-FC3FE7104BBB}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3302,10 +3268,10 @@
               </x14:cfvo>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>F12:F19</xm:sqref>
+          <xm:sqref>I13:I27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9C0BAB09-3951-4C45-81C3-5E0E334A7CFA}">
+          <x14:cfRule type="dataBar" id="{25CF9E22-CE5E-445F-A44D-B79B8DAC43A1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3315,10 +3281,10 @@
               </x14:cfvo>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M12:M16</xm:sqref>
+          <xm:sqref>I32:I36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E2A53AFF-9032-4773-981D-A77642FF4DB7}">
+          <x14:cfRule type="dataBar" id="{54681967-0840-4500-AD8C-E20FB4BA98A2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3328,10 +3294,10 @@
               </x14:cfvo>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M21:M35</xm:sqref>
+          <xm:sqref>Q13:Q20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3F700B6D-9D8A-4367-B352-D75AC487BD9B}">
+          <x14:cfRule type="dataBar" id="{C3C1AD25-AE66-42ED-BA09-341FB0F71CDD}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3341,7 +3307,7 @@
               </x14:cfvo>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C24:C31</xm:sqref>
+          <xm:sqref>M25:M32</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3350,7 +3316,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCC6578-B0F7-44E9-AB44-17B4843E0015}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E29D53-7DA7-496D-9574-91EDC903394C}">
   <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3358,44 +3324,45 @@
     <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="3" max="5" width="13.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" style="2" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" style="4" customWidth="1"/>
     <col min="11" max="11" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" s="6" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3427,7 +3394,7 @@
       <c r="I2" s="2">
         <v>1</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3463,7 +3430,7 @@
       <c r="I3" s="2">
         <v>1</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3496,7 +3463,7 @@
       <c r="I4" s="2">
         <v>1</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3532,7 +3499,7 @@
       <c r="I5" s="2">
         <v>1</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3565,7 +3532,7 @@
       <c r="I6" s="2">
         <v>1</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3598,7 +3565,7 @@
       <c r="I7" s="2">
         <v>0.7</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3634,7 +3601,7 @@
       <c r="I8" s="2">
         <v>0.6</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3667,7 +3634,7 @@
       <c r="I9" s="2">
         <v>0.4</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3703,7 +3670,7 @@
       <c r="I10" s="2">
         <v>0.8</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3736,7 +3703,7 @@
       <c r="I11" s="2">
         <v>0</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3769,7 +3736,7 @@
       <c r="I12" s="2">
         <v>0.5</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3802,7 +3769,7 @@
       <c r="I13" s="2">
         <v>0.3</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3838,7 +3805,7 @@
       <c r="I14" s="2">
         <v>0.9</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3871,7 +3838,7 @@
       <c r="I15" s="2">
         <v>0.75</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3904,7 +3871,7 @@
       <c r="I16" s="2">
         <v>0</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3937,7 +3904,7 @@
       <c r="I17" s="2">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -3970,7 +3937,7 @@
       <c r="I18" s="2">
         <v>0.35</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4003,7 +3970,7 @@
       <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4036,7 +4003,7 @@
       <c r="I20" s="2">
         <v>1</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4072,7 +4039,7 @@
       <c r="I21" s="2">
         <v>0.45</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4105,7 +4072,7 @@
       <c r="I22" s="2">
         <v>0</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J22" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4138,7 +4105,7 @@
       <c r="I23" s="2">
         <v>0</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4171,7 +4138,7 @@
       <c r="I24" s="2">
         <v>0.2</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4207,7 +4174,7 @@
       <c r="I25" s="2">
         <v>0.25</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J25" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4240,7 +4207,7 @@
       <c r="I26" s="2">
         <v>0.4</v>
       </c>
-      <c r="J26" s="4">
+      <c r="J26" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4273,7 +4240,7 @@
       <c r="I27" s="2">
         <v>0.3</v>
       </c>
-      <c r="J27" s="4">
+      <c r="J27" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4306,7 +4273,7 @@
       <c r="I28" s="2">
         <v>0</v>
       </c>
-      <c r="J28" s="4">
+      <c r="J28" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4339,7 +4306,7 @@
       <c r="I29" s="2">
         <v>0.15</v>
       </c>
-      <c r="J29" s="4">
+      <c r="J29" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4372,7 +4339,7 @@
       <c r="I30" s="2">
         <v>0</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4405,7 +4372,7 @@
       <c r="I31" s="2">
         <v>0.2</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J31" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4438,7 +4405,7 @@
       <c r="I32" s="2">
         <v>0.1</v>
       </c>
-      <c r="J32" s="4">
+      <c r="J32" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4474,7 +4441,7 @@
       <c r="I33" s="2">
         <v>0</v>
       </c>
-      <c r="J33" s="4">
+      <c r="J33" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4507,7 +4474,7 @@
       <c r="I34" s="2">
         <v>1</v>
       </c>
-      <c r="J34" s="4">
+      <c r="J34" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4540,7 +4507,7 @@
       <c r="I35" s="2">
         <v>0.1</v>
       </c>
-      <c r="J35" s="4">
+      <c r="J35" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4573,7 +4540,7 @@
       <c r="I36" s="2">
         <v>0</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J36" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4606,7 +4573,7 @@
       <c r="I37" s="2">
         <v>1</v>
       </c>
-      <c r="J37" s="4">
+      <c r="J37" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4639,7 +4606,7 @@
       <c r="I38" s="2">
         <v>1</v>
       </c>
-      <c r="J38" s="4">
+      <c r="J38" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2026</v>
       </c>
@@ -4672,7 +4639,7 @@
       <c r="I39" s="2">
         <v>0</v>
       </c>
-      <c r="J39" s="4">
+      <c r="J39" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2027</v>
       </c>
@@ -4705,7 +4672,7 @@
       <c r="I40" s="2">
         <v>0</v>
       </c>
-      <c r="J40" s="4">
+      <c r="J40" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2027</v>
       </c>
@@ -4738,7 +4705,7 @@
       <c r="I41" s="2">
         <v>0</v>
       </c>
-      <c r="J41" s="4">
+      <c r="J41" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2027</v>
       </c>
@@ -4771,7 +4738,7 @@
       <c r="I42" s="2">
         <v>0</v>
       </c>
-      <c r="J42" s="4">
+      <c r="J42" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2027</v>
       </c>
@@ -4804,7 +4771,7 @@
       <c r="I43" s="2">
         <v>0.05</v>
       </c>
-      <c r="J43" s="4">
+      <c r="J43" s="10">
         <f>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</f>
         <v>2027</v>
       </c>
@@ -4814,73 +4781,36 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="expression" dxfId="12" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
       <formula>AND(ISNUMBER($H1),$H1&lt;TODAY(),$E1&lt;&gt;"Done")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
       <formula>AND(ISNUMBER($H1),$H1&gt;=TODAY(),$H1&lt;=TODAY()+6,$E1&lt;&gt;"Done")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="10" priority="3" stopIfTrue="1">
-      <formula>AND(ISNUMBER($H1),$H1&lt;TODAY(),$E1&lt;&gt;"Done")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF7FB2E5"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1FDDE4AB-3092-4AC6-9168-59577D9F5FC8}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Status" error="Pick one of: Not started, In progress, Blocked, Done" sqref="E2:E43" xr:uid="{133A91FC-F3FD-49C7-82A5-59021248B25F}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Status" error="Pick one of: Not started, In progress, Blocked, Done" sqref="E2:E43" xr:uid="{489FB4ED-78EE-4EAF-BA4F-29FF421A5E55}">
       <formula1>"Not started,In progress,Blocked,Done"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Priority" error="Pick one of: High, Medium, Low" sqref="F2:F43" xr:uid="{6DA95F94-2607-4679-A5DD-F0786E94DB1B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Priority" error="Pick one of: High, Medium, Low" sqref="F2:F43" xr:uid="{DC4C2EF8-47B8-4000-B5A7-7781B7C1AFB7}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="% Complete" error="Type a percentage from 0% to 100%." sqref="I2:I43" xr:uid="{A2E7D993-32A2-429A-A9C7-DD9D343185E9}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="% Complete" error="Type a percentage from 0% to 100%." sqref="I2:I43" xr:uid="{17A0DE7D-172C-476A-ABB0-6A858CB2A8E6}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Year" prompt="Calculated: fills itself in from Due. No need to type here." sqref="J2:J43" xr:uid="{49644272-0EEF-432C-8DF6-DFD975428AA1}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1FDDE4AB-3092-4AC6-9168-59577D9F5FC8}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I1:I1048576</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E397071-473B-4F9C-A6DF-06E068318C4F}">
-  <dimension ref="B2:C30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B8A97E-0897-4869-9F80-D3A8E4EEEED7}">
+  <dimension ref="B1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -4888,14 +4818,15 @@
     <col min="3" max="3" width="112.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="58" t="s">
+    <row r="1" spans="2:3" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="39" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="38" t="s">
         <v>153</v>
       </c>
     </row>
@@ -4903,12 +4834,12 @@
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="40" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="60">
+      <c r="B6" s="41">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -4916,7 +4847,7 @@
       </c>
     </row>
     <row r="7" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="60">
+      <c r="B7" s="41">
         <v>2</v>
       </c>
       <c r="C7" t="s">
@@ -4924,7 +4855,7 @@
       </c>
     </row>
     <row r="8" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="60">
+      <c r="B8" s="41">
         <v>3</v>
       </c>
       <c r="C8" t="s">
@@ -4935,12 +4866,12 @@
       <c r="B9" s="3"/>
     </row>
     <row r="10" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="40" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="60">
+      <c r="B11" s="41">
         <v>4</v>
       </c>
       <c r="C11" t="s">
@@ -4948,7 +4879,7 @@
       </c>
     </row>
     <row r="12" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="60">
+      <c r="B12" s="41">
         <v>5</v>
       </c>
       <c r="C12" t="s">
@@ -4956,7 +4887,7 @@
       </c>
     </row>
     <row r="13" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="60">
+      <c r="B13" s="41">
         <v>6</v>
       </c>
       <c r="C13" t="s">
@@ -4964,7 +4895,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="60">
+      <c r="B14" s="41">
         <v>7</v>
       </c>
       <c r="C14" t="s">
@@ -4975,12 +4906,12 @@
       <c r="B15" s="3"/>
     </row>
     <row r="16" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="40" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="60">
+      <c r="B17" s="41">
         <v>8</v>
       </c>
       <c r="C17" t="s">
@@ -4988,7 +4919,7 @@
       </c>
     </row>
     <row r="18" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="60">
+      <c r="B18" s="41">
         <v>9</v>
       </c>
       <c r="C18" t="s">
@@ -4996,7 +4927,7 @@
       </c>
     </row>
     <row r="19" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="60">
+      <c r="B19" s="41">
         <v>10</v>
       </c>
       <c r="C19" t="s">
@@ -5042,9 +4973,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8990AE33-E0AE-4D13-819F-52BA89674BA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5635006D-7825-4AB4-BCB0-0E46EA8A39F4}">
   <sheetPr>
-    <tabColor rgb="FFB8C0CC"/>
+    <tabColor rgb="FF5B6B7F"/>
   </sheetPr>
   <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5069,50 +5000,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="12" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="13" t="s">
         <v>130</v>
       </c>
     </row>
@@ -5129,7 +5060,7 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G4),"")</f>
         <v>46297.00013</v>
       </c>
@@ -5140,7 +5071,7 @@
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondUpcoming,$K4),"")</f>
         <v>46297.00013</v>
       </c>
@@ -5151,7 +5082,7 @@
       <c r="O4">
         <v>1</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P4" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O4),"")</f>
         <v>46282.000119999997</v>
       </c>
@@ -5175,7 +5106,7 @@
       <c r="G5">
         <v>2</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G5),"")</f>
         <v>46298.000139999996</v>
       </c>
@@ -5186,7 +5117,7 @@
       <c r="K5">
         <v>2</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondUpcoming,$K5),"")</f>
         <v>46298.000139999996</v>
       </c>
@@ -5197,7 +5128,7 @@
       <c r="O5">
         <v>2</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O5),"")</f>
         <v>46285.000059999998</v>
       </c>
@@ -5221,7 +5152,7 @@
       <c r="G6">
         <v>3</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G6),"")</f>
         <v>46299.00015</v>
       </c>
@@ -5232,7 +5163,7 @@
       <c r="K6">
         <v>3</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondUpcoming,$K6),"")</f>
         <v>46299.00015</v>
       </c>
@@ -5243,7 +5174,7 @@
       <c r="O6">
         <v>3</v>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O6),"")</f>
         <v>46289.000070000002</v>
       </c>
@@ -5267,7 +5198,7 @@
       <c r="G7">
         <v>4</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G7),"")</f>
         <v>46300.000160000003</v>
       </c>
@@ -5278,7 +5209,7 @@
       <c r="K7">
         <v>4</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondUpcoming,$K7),"")</f>
         <v>46300.000160000003</v>
       </c>
@@ -5289,7 +5220,7 @@
       <c r="O7">
         <v>4</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O7),"")</f>
         <v>46291.000079999998</v>
       </c>
@@ -5313,7 +5244,7 @@
       <c r="G8">
         <v>5</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G8),"")</f>
         <v>46302.000169999999</v>
       </c>
@@ -5324,7 +5255,7 @@
       <c r="K8">
         <v>5</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondUpcoming,$K8),"")</f>
         <v>46302.000169999999</v>
       </c>
@@ -5335,7 +5266,7 @@
       <c r="O8">
         <v>5</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O8),"")</f>
         <v>46293.000090000001</v>
       </c>
@@ -5356,7 +5287,7 @@
       <c r="G9">
         <v>6</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G9),"")</f>
         <v>46303.000180000003</v>
       </c>
@@ -5367,7 +5298,7 @@
       <c r="O9">
         <v>6</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O9),"")</f>
         <v>46295.000099999997</v>
       </c>
@@ -5388,7 +5319,7 @@
       <c r="G10">
         <v>7</v>
       </c>
-      <c r="H10" s="8" t="str">
+      <c r="H10" s="14" t="str">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G10),"")</f>
         <v/>
       </c>
@@ -5399,7 +5330,7 @@
       <c r="O10">
         <v>7</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O10),"")</f>
         <v>46296.000110000001</v>
       </c>
@@ -5420,7 +5351,7 @@
       <c r="G11">
         <v>8</v>
       </c>
-      <c r="H11" s="8" t="str">
+      <c r="H11" s="14" t="str">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G11),"")</f>
         <v/>
       </c>
@@ -5431,7 +5362,7 @@
       <c r="O11">
         <v>8</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O11),"")</f>
         <v>46297.00013</v>
       </c>
@@ -5452,7 +5383,7 @@
       <c r="O12">
         <v>9</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O12),"")</f>
         <v>46298.000139999996</v>
       </c>
@@ -5473,7 +5404,7 @@
       <c r="O13">
         <v>10</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P13" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O13),"")</f>
         <v>46299.00015</v>
       </c>
@@ -5494,7 +5425,7 @@
       <c r="O14">
         <v>11</v>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O14),"")</f>
         <v>46300.000160000003</v>
       </c>
@@ -5511,7 +5442,7 @@
       <c r="O15">
         <v>12</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O15),"")</f>
         <v>46302.000169999999</v>
       </c>
@@ -5528,7 +5459,7 @@
       <c r="O16">
         <v>13</v>
       </c>
-      <c r="P16" s="8">
+      <c r="P16" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O16),"")</f>
         <v>46303.000180000003</v>
       </c>
@@ -5545,7 +5476,7 @@
       <c r="O17">
         <v>14</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P17" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O17),"")</f>
         <v>46304.000200000002</v>
       </c>
@@ -5562,7 +5493,7 @@
       <c r="O18">
         <v>15</v>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O18),"")</f>
         <v>46305.000209999998</v>
       </c>

--- a/deliverable/Work Tracker Demo.xlsx
+++ b/deliverable/Work Tracker Demo.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8C046DA-E49E-4C7E-B805-181713F9980E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBCB23F0-C766-4B66-9BCA-B2DA2543DB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9621E1EE-779C-450F-87AC-5CDFDDD3B01E}"/>
+    <workbookView xWindow="0" yWindow="1305" windowWidth="21600" windowHeight="11520" xr2:uid="{1F9FEBDE-B559-42F3-97A0-796F3DC4A106}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -548,13 +548,13 @@
     <t>Good to know</t>
   </si>
   <si>
-    <t>Nothing here needs macros. The file works in Excel 2010 and later, including Microsoft 365.</t>
+    <t>Nothing here needs macros. It uses formulas that exist in Excel 2010 and later; built and tested in Excel for Microsoft 365 on Windows.</t>
   </si>
   <si>
     <t>The Lists sheet holds helper formulas for the dashboard. Leave it as it is.</t>
   </si>
   <si>
-    <t>The sample dates were set on Oct 2, 2026, so some tasks were overdue and some due that week. The dashboard always compares with today's date, so the counts move as days pass.</t>
+    <t>The sample dates were set on Oct 6, 2026, so some tasks were overdue and some due that week. The dashboard always compares with today's date, so the counts move as days pass.</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1010,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="AZG Table" pivot="0" table="0" count="2" xr9:uid="{152807FA-F056-43F9-8DBA-FF331AEB0691}">
+    <tableStyle name="AZG Table" pivot="0" table="0" count="2" xr9:uid="{A2000176-35D8-4FC9-8680-BCB2C491144B}">
       <tableStyleElement type="wholeTable" dxfId="19"/>
       <tableStyleElement type="headerRow" dxfId="18"/>
     </tableStyle>
@@ -1027,22 +1027,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49590DEB-0070-423E-982E-B237A19237B5}" name="Tasks" displayName="Tasks" ref="A1:K43" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="A1:K43" xr:uid="{49590DEB-0070-423E-982E-B237A19237B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C309CA55-1D5B-4171-95B2-225A5B757F40}" name="Tasks" displayName="Tasks" ref="A1:K43" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="A1:K43" xr:uid="{C309CA55-1D5B-4171-95B2-225A5B757F40}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F7799466-306B-4085-88A3-9BAFC2E2963B}" name="ID" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{515B7545-E5A6-4900-BB7B-2FBE4FB6AAAF}" name="Task"/>
-    <tableColumn id="3" xr3:uid="{B35098B6-DA25-4832-AEA0-570CE5C79917}" name="Owner"/>
-    <tableColumn id="4" xr3:uid="{A2138601-112D-4AC2-B4EE-BE5361088E3A}" name="Department"/>
-    <tableColumn id="5" xr3:uid="{F0814445-79E8-4D6E-834F-EB0C3725F3D6}" name="Status"/>
-    <tableColumn id="6" xr3:uid="{2E7DEBD4-F428-4726-B2CF-4B4DE5C6E0BE}" name="Priority"/>
-    <tableColumn id="7" xr3:uid="{E80337C6-3463-456A-B55A-DCB248D25985}" name="Start" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{5E3602ED-F95C-4854-BA13-F13471ACD221}" name="Due" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{81E0FB5F-7848-475F-8608-DF0EBF9C3069}" name="% Complete" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{5E664E38-2C8D-4F49-88D8-0A7E555C94E1}" name="Year" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{95AE37A2-8FAF-401A-B1E7-3C4D9F4C769C}" name="ID" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{7C6E9FE7-90F0-4387-AA2D-FFB5CBE04370}" name="Task"/>
+    <tableColumn id="3" xr3:uid="{D26EEC67-5C02-42A3-9CD5-9586411A4B4F}" name="Owner"/>
+    <tableColumn id="4" xr3:uid="{6CC9D32B-6B50-4C3A-9D8F-EAF44DE4BC33}" name="Department"/>
+    <tableColumn id="5" xr3:uid="{57DD70EF-1F9B-44E5-A5F3-9A29FFD7F595}" name="Status"/>
+    <tableColumn id="6" xr3:uid="{9ED822FD-A86B-4DA2-BE22-0869F8E3A98E}" name="Priority"/>
+    <tableColumn id="7" xr3:uid="{0E7840EE-FBBE-42DE-BC77-A61A12EA26FA}" name="Start" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{60854EE4-9596-44B4-9B30-43C6545612F8}" name="Due" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{94837B56-72C6-47E5-88CD-4FE62E94847D}" name="% Complete" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{5EB4190D-2789-47DC-ADDE-D5641105789D}" name="Year" dataDxfId="12">
       <calculatedColumnFormula>IF(Tasks[[#This Row],[Due]]="","",YEAR(Tasks[[#This Row],[Due]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{1DD86DAE-03BB-432E-82AB-37C133F30EC1}" name="Notes"/>
+    <tableColumn id="11" xr3:uid="{28387B19-2D1A-41E3-AE15-9A1E0CB32EB6}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="AZG Table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1344,7 +1344,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11EDC162-3DBE-44AD-8899-AC75CDC4CA74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D28430-7EC2-42C2-B6D5-BD508157B9BC}">
   <sheetPr>
     <tabColor rgb="FF1F3A5F"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1418,7 +1418,7 @@
       <c r="A3" s="6"/>
       <c r="B3" s="16" t="str">
         <f ca="1">"As of "&amp;TEXT(TODAY(),"ddd, mmm d, yyyy")&amp;"   |   Pick an owner, status or year: the whole page follows."</f>
-        <v>As of Fri, Oct 2, 2026   |   Pick an owner, status or year: the whole page follows.</v>
+        <v>As of Tue, Oct 6, 2026   |   Pick an owner, status or year: the whole page follows.</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1696,7 +1696,7 @@
       <c r="A13" s="6"/>
       <c r="B13" s="33">
         <f>IF(Lists!$Q4="","",IF(MOD(INT(Lists!$P4),100000)=99999,"",MOD(INT(Lists!$P4),100000)))</f>
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C13" s="6" t="str">
         <f>IF(Lists!$Q4="","No tasks match these filters",INDEX(Tasks[Task],Lists!$Q4)&amp;"")</f>
@@ -1733,7 +1733,7 @@
       <c r="K13" s="6"/>
       <c r="L13" s="33">
         <f ca="1">IF(Lists!$I4="","",INT(Lists!$H4))</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="M13" s="6" t="str">
         <f ca="1">IF(Lists!$I4="","Nothing due in the next 7 days",INDEX(Tasks[Task],Lists!$I4)&amp;"")</f>
@@ -1761,7 +1761,7 @@
       <c r="A14" s="6"/>
       <c r="B14" s="33">
         <f>IF(Lists!$Q5="","",IF(MOD(INT(Lists!$P5),100000)=99999,"",MOD(INT(Lists!$P5),100000)))</f>
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="C14" s="6" t="str">
         <f>IF(Lists!$Q5="","",INDEX(Tasks[Task],Lists!$Q5)&amp;"")</f>
@@ -1798,7 +1798,7 @@
       <c r="K14" s="6"/>
       <c r="L14" s="33">
         <f ca="1">IF(Lists!$I5="","",INT(Lists!$H5))</f>
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="M14" s="6" t="str">
         <f ca="1">IF(Lists!$I5="","",INDEX(Tasks[Task],Lists!$I5)&amp;"")</f>
@@ -1826,7 +1826,7 @@
       <c r="A15" s="6"/>
       <c r="B15" s="33">
         <f>IF(Lists!$Q6="","",IF(MOD(INT(Lists!$P6),100000)=99999,"",MOD(INT(Lists!$P6),100000)))</f>
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="C15" s="6" t="str">
         <f>IF(Lists!$Q6="","",INDEX(Tasks[Task],Lists!$Q6)&amp;"")</f>
@@ -1863,7 +1863,7 @@
       <c r="K15" s="6"/>
       <c r="L15" s="33">
         <f ca="1">IF(Lists!$I6="","",INT(Lists!$H6))</f>
-        <v>46299</v>
+        <v>46303</v>
       </c>
       <c r="M15" s="6" t="str">
         <f ca="1">IF(Lists!$I6="","",INDEX(Tasks[Task],Lists!$I6)&amp;"")</f>
@@ -1891,7 +1891,7 @@
       <c r="A16" s="6"/>
       <c r="B16" s="33">
         <f>IF(Lists!$Q7="","",IF(MOD(INT(Lists!$P7),100000)=99999,"",MOD(INT(Lists!$P7),100000)))</f>
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C16" s="6" t="str">
         <f>IF(Lists!$Q7="","",INDEX(Tasks[Task],Lists!$Q7)&amp;"")</f>
@@ -1928,7 +1928,7 @@
       <c r="K16" s="6"/>
       <c r="L16" s="33">
         <f ca="1">IF(Lists!$I7="","",INT(Lists!$H7))</f>
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="M16" s="6" t="str">
         <f ca="1">IF(Lists!$I7="","",INDEX(Tasks[Task],Lists!$I7)&amp;"")</f>
@@ -1956,7 +1956,7 @@
       <c r="A17" s="6"/>
       <c r="B17" s="33">
         <f>IF(Lists!$Q8="","",IF(MOD(INT(Lists!$P8),100000)=99999,"",MOD(INT(Lists!$P8),100000)))</f>
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C17" s="6" t="str">
         <f>IF(Lists!$Q8="","",INDEX(Tasks[Task],Lists!$Q8)&amp;"")</f>
@@ -1993,7 +1993,7 @@
       <c r="K17" s="6"/>
       <c r="L17" s="33">
         <f ca="1">IF(Lists!$I8="","",INT(Lists!$H8))</f>
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="M17" s="6" t="str">
         <f ca="1">IF(Lists!$I8="","",INDEX(Tasks[Task],Lists!$I8)&amp;"")</f>
@@ -2021,7 +2021,7 @@
       <c r="A18" s="6"/>
       <c r="B18" s="33">
         <f>IF(Lists!$Q9="","",IF(MOD(INT(Lists!$P9),100000)=99999,"",MOD(INT(Lists!$P9),100000)))</f>
-        <v>46295</v>
+        <v>46299</v>
       </c>
       <c r="C18" s="6" t="str">
         <f>IF(Lists!$Q9="","",INDEX(Tasks[Task],Lists!$Q9)&amp;"")</f>
@@ -2058,7 +2058,7 @@
       <c r="K18" s="6"/>
       <c r="L18" s="33">
         <f ca="1">IF(Lists!$I9="","",INT(Lists!$H9))</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="M18" s="6" t="str">
         <f ca="1">IF(Lists!$I9="","",INDEX(Tasks[Task],Lists!$I9)&amp;"")</f>
@@ -2086,7 +2086,7 @@
       <c r="A19" s="6"/>
       <c r="B19" s="33">
         <f>IF(Lists!$Q10="","",IF(MOD(INT(Lists!$P10),100000)=99999,"",MOD(INT(Lists!$P10),100000)))</f>
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="C19" s="6" t="str">
         <f>IF(Lists!$Q10="","",INDEX(Tasks[Task],Lists!$Q10)&amp;"")</f>
@@ -2151,7 +2151,7 @@
       <c r="A20" s="6"/>
       <c r="B20" s="33">
         <f>IF(Lists!$Q11="","",IF(MOD(INT(Lists!$P11),100000)=99999,"",MOD(INT(Lists!$P11),100000)))</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C20" s="6" t="str">
         <f>IF(Lists!$Q11="","",INDEX(Tasks[Task],Lists!$Q11)&amp;"")</f>
@@ -2216,7 +2216,7 @@
       <c r="A21" s="6"/>
       <c r="B21" s="33">
         <f>IF(Lists!$Q12="","",IF(MOD(INT(Lists!$P12),100000)=99999,"",MOD(INT(Lists!$P12),100000)))</f>
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="C21" s="6" t="str">
         <f>IF(Lists!$Q12="","",INDEX(Tasks[Task],Lists!$Q12)&amp;"")</f>
@@ -2266,7 +2266,7 @@
       <c r="A22" s="6"/>
       <c r="B22" s="33">
         <f>IF(Lists!$Q13="","",IF(MOD(INT(Lists!$P13),100000)=99999,"",MOD(INT(Lists!$P13),100000)))</f>
-        <v>46299</v>
+        <v>46303</v>
       </c>
       <c r="C22" s="6" t="str">
         <f>IF(Lists!$Q13="","",INDEX(Tasks[Task],Lists!$Q13)&amp;"")</f>
@@ -2313,7 +2313,7 @@
       <c r="A23" s="6"/>
       <c r="B23" s="33">
         <f>IF(Lists!$Q14="","",IF(MOD(INT(Lists!$P14),100000)=99999,"",MOD(INT(Lists!$P14),100000)))</f>
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="C23" s="6" t="str">
         <f>IF(Lists!$Q14="","",INDEX(Tasks[Task],Lists!$Q14)&amp;"")</f>
@@ -2364,7 +2364,7 @@
       <c r="A24" s="6"/>
       <c r="B24" s="33">
         <f>IF(Lists!$Q15="","",IF(MOD(INT(Lists!$P15),100000)=99999,"",MOD(INT(Lists!$P15),100000)))</f>
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="C24" s="6" t="str">
         <f>IF(Lists!$Q15="","",INDEX(Tasks[Task],Lists!$Q15)&amp;"")</f>
@@ -2421,7 +2421,7 @@
       <c r="A25" s="6"/>
       <c r="B25" s="33">
         <f>IF(Lists!$Q16="","",IF(MOD(INT(Lists!$P16),100000)=99999,"",MOD(INT(Lists!$P16),100000)))</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C25" s="6" t="str">
         <f>IF(Lists!$Q16="","",INDEX(Tasks[Task],Lists!$Q16)&amp;"")</f>
@@ -2486,7 +2486,7 @@
       <c r="A26" s="6"/>
       <c r="B26" s="33">
         <f>IF(Lists!$Q17="","",IF(MOD(INT(Lists!$P17),100000)=99999,"",MOD(INT(Lists!$P17),100000)))</f>
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="C26" s="6" t="str">
         <f>IF(Lists!$Q17="","",INDEX(Tasks[Task],Lists!$Q17)&amp;"")</f>
@@ -2551,7 +2551,7 @@
       <c r="A27" s="6"/>
       <c r="B27" s="33">
         <f>IF(Lists!$Q18="","",IF(MOD(INT(Lists!$P18),100000)=99999,"",MOD(INT(Lists!$P18),100000)))</f>
-        <v>46305</v>
+        <v>46309</v>
       </c>
       <c r="C27" s="6" t="str">
         <f>IF(Lists!$Q18="","",INDEX(Tasks[Task],Lists!$Q18)&amp;"")</f>
@@ -2791,7 +2791,7 @@
       <c r="A32" s="6"/>
       <c r="B32" s="33">
         <f ca="1">IF(Lists!$M4="","",INT(Lists!$L4))</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C32" s="6" t="str">
         <f ca="1">IF(Lists!$M4="","Nothing coming up",INDEX(Tasks[Task],Lists!$M4)&amp;"")</f>
@@ -2856,7 +2856,7 @@
       <c r="A33" s="6"/>
       <c r="B33" s="33">
         <f ca="1">IF(Lists!$M5="","",INT(Lists!$L5))</f>
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="C33" s="6" t="str">
         <f ca="1">IF(Lists!$M5="","",INDEX(Tasks[Task],Lists!$M5)&amp;"")</f>
@@ -2906,7 +2906,7 @@
       <c r="A34" s="6"/>
       <c r="B34" s="33">
         <f ca="1">IF(Lists!$M6="","",INT(Lists!$L6))</f>
-        <v>46299</v>
+        <v>46303</v>
       </c>
       <c r="C34" s="6" t="str">
         <f ca="1">IF(Lists!$M6="","",INDEX(Tasks[Task],Lists!$M6)&amp;"")</f>
@@ -2953,7 +2953,7 @@
       <c r="A35" s="6"/>
       <c r="B35" s="33">
         <f ca="1">IF(Lists!$M7="","",INT(Lists!$L7))</f>
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="C35" s="6" t="str">
         <f ca="1">IF(Lists!$M7="","",INDEX(Tasks[Task],Lists!$M7)&amp;"")</f>
@@ -3000,7 +3000,7 @@
       <c r="A36" s="6"/>
       <c r="B36" s="33">
         <f ca="1">IF(Lists!$M8="","",INT(Lists!$L8))</f>
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="C36" s="6" t="str">
         <f ca="1">IF(Lists!$M8="","",INDEX(Tasks[Task],Lists!$M8)&amp;"")</f>
@@ -3150,7 +3150,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E35422CB-ABC0-43BF-B8A7-FC3FE7104BBB}</x14:id>
+          <x14:id>{7DD9ADC7-A4BA-45BD-98C0-7C2567430AB9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3164,7 +3164,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25CF9E22-CE5E-445F-A44D-B79B8DAC43A1}</x14:id>
+          <x14:id>{DC98CC5B-160A-4530-85D9-83CF12364E09}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3178,7 +3178,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{54681967-0840-4500-AD8C-E20FB4BA98A2}</x14:id>
+          <x14:id>{370AFC6A-8E62-419C-8606-93946B24281C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3192,7 +3192,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C3C1AD25-AE66-42ED-BA09-341FB0F71CDD}</x14:id>
+          <x14:id>{D66F7962-E0DF-4356-B2EA-FDF4FA35A640}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3242,13 +3242,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Owner" error="Pick a value from the list." sqref="C5" xr:uid="{4B2C24AC-35A5-4D3C-832A-AD0FB8D99A49}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Owner" error="Pick a value from the list." sqref="C5" xr:uid="{2652F965-A0B3-4ED3-98B7-D7A935E9CCD3}">
       <formula1>OwnerList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Status" error="Pick a value from the list." sqref="E5" xr:uid="{8C4DEA33-04EC-4DEB-8BB7-BFEE728A8E1B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Status" error="Pick a value from the list." sqref="E5" xr:uid="{F0C7AC77-2C2D-4B0B-88B1-EAE13F3A3DD7}">
       <formula1>StatusList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Year" error="Pick a value from the list." sqref="H5" xr:uid="{86F91568-DA26-4F57-BE09-E76E98A91480}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Year" error="Pick a value from the list." sqref="H5" xr:uid="{C9CA92E9-D5EB-4A63-9DE9-FC9D72EB48BD}">
       <formula1>YearList</formula1>
     </dataValidation>
   </dataValidations>
@@ -3258,7 +3258,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E35422CB-ABC0-43BF-B8A7-FC3FE7104BBB}">
+          <x14:cfRule type="dataBar" id="{7DD9ADC7-A4BA-45BD-98C0-7C2567430AB9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3271,7 +3271,7 @@
           <xm:sqref>I13:I27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{25CF9E22-CE5E-445F-A44D-B79B8DAC43A1}">
+          <x14:cfRule type="dataBar" id="{DC98CC5B-160A-4530-85D9-83CF12364E09}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3284,7 +3284,7 @@
           <xm:sqref>I32:I36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{54681967-0840-4500-AD8C-E20FB4BA98A2}">
+          <x14:cfRule type="dataBar" id="{370AFC6A-8E62-419C-8606-93946B24281C}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3297,7 +3297,7 @@
           <xm:sqref>Q13:Q20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C3C1AD25-AE66-42ED-BA09-341FB0F71CDD}">
+          <x14:cfRule type="dataBar" id="{D66F7962-E0DF-4356-B2EA-FDF4FA35A640}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3316,7 +3316,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E29D53-7DA7-496D-9574-91EDC903394C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE5E477B-3042-48D3-B78B-9A2FD1A0E76A}">
   <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3386,10 +3386,10 @@
         <v>16</v>
       </c>
       <c r="G2" s="1">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="H2" s="1">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="I2" s="2">
         <v>1</v>
@@ -3422,10 +3422,10 @@
         <v>16</v>
       </c>
       <c r="G3" s="1">
-        <v>46252</v>
+        <v>46256</v>
       </c>
       <c r="H3" s="1">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="I3" s="2">
         <v>1</v>
@@ -3455,10 +3455,10 @@
         <v>26</v>
       </c>
       <c r="G4" s="1">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="H4" s="1">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
@@ -3491,10 +3491,10 @@
         <v>32</v>
       </c>
       <c r="G5" s="1">
-        <v>46267</v>
+        <v>46271</v>
       </c>
       <c r="H5" s="1">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -3524,10 +3524,10 @@
         <v>26</v>
       </c>
       <c r="G6" s="1">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="H6" s="1">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -3557,10 +3557,10 @@
         <v>16</v>
       </c>
       <c r="G7" s="1">
-        <v>46267</v>
+        <v>46271</v>
       </c>
       <c r="H7" s="1">
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="I7" s="2">
         <v>0.7</v>
@@ -3593,10 +3593,10 @@
         <v>26</v>
       </c>
       <c r="G8" s="1">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="H8" s="1">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="I8" s="2">
         <v>0.6</v>
@@ -3626,10 +3626,10 @@
         <v>16</v>
       </c>
       <c r="G9" s="1">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="H9" s="1">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="I9" s="2">
         <v>0.4</v>
@@ -3662,10 +3662,10 @@
         <v>26</v>
       </c>
       <c r="G10" s="1">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H10" s="1">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="I10" s="2">
         <v>0.8</v>
@@ -3695,10 +3695,10 @@
         <v>16</v>
       </c>
       <c r="G11" s="1">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="H11" s="1">
-        <v>46295</v>
+        <v>46299</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
@@ -3728,10 +3728,10 @@
         <v>16</v>
       </c>
       <c r="G12" s="1">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="H12" s="1">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="I12" s="2">
         <v>0.5</v>
@@ -3761,10 +3761,10 @@
         <v>26</v>
       </c>
       <c r="G13" s="1">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="H13" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="I13" s="2">
         <v>0.3</v>
@@ -3797,10 +3797,10 @@
         <v>26</v>
       </c>
       <c r="G14" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="H14" s="1">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="I14" s="2">
         <v>0.9</v>
@@ -3830,10 +3830,10 @@
         <v>32</v>
       </c>
       <c r="G15" s="1">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="H15" s="1">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="I15" s="2">
         <v>0.75</v>
@@ -3863,10 +3863,10 @@
         <v>16</v>
       </c>
       <c r="G16" s="1">
-        <v>46295</v>
+        <v>46299</v>
       </c>
       <c r="H16" s="1">
-        <v>46299</v>
+        <v>46303</v>
       </c>
       <c r="I16" s="2">
         <v>0</v>
@@ -3896,10 +3896,10 @@
         <v>26</v>
       </c>
       <c r="G17" s="1">
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="H17" s="1">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="I17" s="2">
         <v>0.55000000000000004</v>
@@ -3929,10 +3929,10 @@
         <v>16</v>
       </c>
       <c r="G18" s="1">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="H18" s="1">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="I18" s="2">
         <v>0.35</v>
@@ -3962,10 +3962,10 @@
         <v>16</v>
       </c>
       <c r="G19" s="1">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="H19" s="1">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="I19" s="2">
         <v>0</v>
@@ -3995,10 +3995,10 @@
         <v>26</v>
       </c>
       <c r="G20" s="1">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="H20" s="1">
-        <v>46299</v>
+        <v>46303</v>
       </c>
       <c r="I20" s="2">
         <v>1</v>
@@ -4031,10 +4031,10 @@
         <v>16</v>
       </c>
       <c r="G21" s="1">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="H21" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="I21" s="2">
         <v>0.45</v>
@@ -4064,10 +4064,10 @@
         <v>26</v>
       </c>
       <c r="G22" s="1">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="H22" s="1">
-        <v>46305</v>
+        <v>46309</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>32</v>
       </c>
       <c r="G23" s="1">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="H23" s="1">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
@@ -4130,10 +4130,10 @@
         <v>16</v>
       </c>
       <c r="G24" s="1">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="H24" s="1">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="I24" s="2">
         <v>0.2</v>
@@ -4166,10 +4166,10 @@
         <v>16</v>
       </c>
       <c r="G25" s="1">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="H25" s="1">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="I25" s="2">
         <v>0.25</v>
@@ -4199,10 +4199,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="1">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="H26" s="1">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="I26" s="2">
         <v>0.4</v>
@@ -4232,10 +4232,10 @@
         <v>16</v>
       </c>
       <c r="G27" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="H27" s="1">
-        <v>46313</v>
+        <v>46317</v>
       </c>
       <c r="I27" s="2">
         <v>0.3</v>
@@ -4265,10 +4265,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="1">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="H28" s="1">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="I28" s="2">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="1">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="H29" s="1">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="I29" s="2">
         <v>0.15</v>
@@ -4331,10 +4331,10 @@
         <v>16</v>
       </c>
       <c r="G30" s="1">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="H30" s="1">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="I30" s="2">
         <v>0</v>
@@ -4364,10 +4364,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="1">
-        <v>46295</v>
+        <v>46299</v>
       </c>
       <c r="H31" s="1">
-        <v>46327</v>
+        <v>46331</v>
       </c>
       <c r="I31" s="2">
         <v>0.2</v>
@@ -4397,10 +4397,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="H32" s="1">
-        <v>46332</v>
+        <v>46336</v>
       </c>
       <c r="I32" s="2">
         <v>0.1</v>
@@ -4433,10 +4433,10 @@
         <v>16</v>
       </c>
       <c r="G33" s="1">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="H33" s="1">
-        <v>46339</v>
+        <v>46343</v>
       </c>
       <c r="I33" s="2">
         <v>0</v>
@@ -4466,10 +4466,10 @@
         <v>32</v>
       </c>
       <c r="G34" s="1">
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="H34" s="1">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
@@ -4499,10 +4499,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="1">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="H35" s="1">
-        <v>46345</v>
+        <v>46349</v>
       </c>
       <c r="I35" s="2">
         <v>0.1</v>
@@ -4532,10 +4532,10 @@
         <v>32</v>
       </c>
       <c r="G36" s="1">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="H36" s="1">
-        <v>46353</v>
+        <v>46357</v>
       </c>
       <c r="I36" s="2">
         <v>0</v>
@@ -4565,10 +4565,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="1">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="H37" s="1">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="I37" s="2">
         <v>1</v>
@@ -4598,10 +4598,10 @@
         <v>16</v>
       </c>
       <c r="G38" s="1">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="H38" s="1">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="I38" s="2">
         <v>1</v>
@@ -4631,10 +4631,10 @@
         <v>16</v>
       </c>
       <c r="G39" s="1">
-        <v>46357</v>
+        <v>46361</v>
       </c>
       <c r="H39" s="1">
-        <v>46392</v>
+        <v>46396</v>
       </c>
       <c r="I39" s="2">
         <v>0</v>
@@ -4664,10 +4664,10 @@
         <v>32</v>
       </c>
       <c r="G40" s="1">
-        <v>46367</v>
+        <v>46371</v>
       </c>
       <c r="H40" s="1">
-        <v>46397</v>
+        <v>46401</v>
       </c>
       <c r="I40" s="2">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="1">
-        <v>46362</v>
+        <v>46366</v>
       </c>
       <c r="H41" s="1">
-        <v>46402</v>
+        <v>46406</v>
       </c>
       <c r="I41" s="2">
         <v>0</v>
@@ -4730,10 +4730,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="1">
-        <v>46377</v>
+        <v>46381</v>
       </c>
       <c r="H42" s="1">
-        <v>46415</v>
+        <v>46419</v>
       </c>
       <c r="I42" s="2">
         <v>0</v>
@@ -4763,10 +4763,10 @@
         <v>32</v>
       </c>
       <c r="G43" s="1">
-        <v>46327</v>
+        <v>46331</v>
       </c>
       <c r="H43" s="1">
-        <v>46422</v>
+        <v>46426</v>
       </c>
       <c r="I43" s="2">
         <v>0.05</v>
@@ -4789,17 +4789,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Status" error="Pick one of: Not started, In progress, Blocked, Done" sqref="E2:E43" xr:uid="{489FB4ED-78EE-4EAF-BA4F-29FF421A5E55}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Status" error="Pick one of: Not started, In progress, Blocked, Done" sqref="E2:E43" xr:uid="{7DD60231-D010-4DEC-BC9F-E510163CA591}">
       <formula1>"Not started,In progress,Blocked,Done"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Priority" error="Pick one of: High, Medium, Low" sqref="F2:F43" xr:uid="{DC4C2EF8-47B8-4000-B5A7-7781B7C1AFB7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Priority" error="Pick one of: High, Medium, Low" sqref="F2:F43" xr:uid="{063D0543-70EA-4E80-BC6B-88278773C6D1}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="% Complete" error="Type a percentage from 0% to 100%." sqref="I2:I43" xr:uid="{17A0DE7D-172C-476A-ABB0-6A858CB2A8E6}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="% Complete" error="Type a percentage from 0% to 100%." sqref="I2:I43" xr:uid="{65C1A00B-3971-4BBB-98F9-F5F8BA6AFB4E}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Year" prompt="Calculated: fills itself in from Due. No need to type here." sqref="J2:J43" xr:uid="{49644272-0EEF-432C-8DF6-DFD975428AA1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Year" prompt="Calculated: fills itself in from Due. No need to type here." sqref="J2:J43" xr:uid="{AFE86B2E-D0E4-450A-B66E-64459ADB78E2}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4809,7 +4809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B8A97E-0897-4869-9F80-D3A8E4EEEED7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1F64F9D-DA22-4008-B9C0-1CC36293FDCE}">
   <dimension ref="B1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4973,7 +4973,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5635006D-7825-4AB4-BCB0-0E46EA8A39F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1CAF32-C6C9-4BF7-B6E5-B4DE9DE86E02}">
   <sheetPr>
     <tabColor rgb="FF5B6B7F"/>
   </sheetPr>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H4" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G4),"")</f>
-        <v>46297.00013</v>
+        <v>46301.00013</v>
       </c>
       <c r="I4">
         <f t="shared" ref="I4:I11" ca="1" si="0">IF(H4="","",ROUND(MOD(H4,1)*100000,0))</f>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="L4" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondUpcoming,$K4),"")</f>
-        <v>46297.00013</v>
+        <v>46301.00013</v>
       </c>
       <c r="M4">
         <f t="shared" ref="M4:M8" ca="1" si="1">IF(L4="","",ROUND(MOD(L4,1)*100000,0))</f>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P4" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O4),"")</f>
-        <v>46282.000119999997</v>
+        <v>46286.000119999997</v>
       </c>
       <c r="Q4">
         <f t="shared" ref="Q4:Q18" si="2">IF(P4="","",ROUND(MOD(P4,1)*100000,0))</f>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="H5" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G5),"")</f>
-        <v>46298.000139999996</v>
+        <v>46302.000139999996</v>
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="0"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="L5" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondUpcoming,$K5),"")</f>
-        <v>46298.000139999996</v>
+        <v>46302.000139999996</v>
       </c>
       <c r="M5">
         <f t="shared" ca="1" si="1"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P5" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O5),"")</f>
-        <v>46285.000059999998</v>
+        <v>46289.000059999998</v>
       </c>
       <c r="Q5">
         <f t="shared" si="2"/>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H6" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G6),"")</f>
-        <v>46299.00015</v>
+        <v>46303.00015</v>
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="0"/>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="L6" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondUpcoming,$K6),"")</f>
-        <v>46299.00015</v>
+        <v>46303.00015</v>
       </c>
       <c r="M6">
         <f t="shared" ca="1" si="1"/>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="P6" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O6),"")</f>
-        <v>46289.000070000002</v>
+        <v>46293.000070000002</v>
       </c>
       <c r="Q6">
         <f t="shared" si="2"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="H7" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G7),"")</f>
-        <v>46300.000160000003</v>
+        <v>46304.000160000003</v>
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="0"/>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="L7" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondUpcoming,$K7),"")</f>
-        <v>46300.000160000003</v>
+        <v>46304.000160000003</v>
       </c>
       <c r="M7">
         <f t="shared" ca="1" si="1"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="P7" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O7),"")</f>
-        <v>46291.000079999998</v>
+        <v>46295.000079999998</v>
       </c>
       <c r="Q7">
         <f t="shared" si="2"/>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H8" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G8),"")</f>
-        <v>46302.000169999999</v>
+        <v>46306.000169999999</v>
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="0"/>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="L8" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondUpcoming,$K8),"")</f>
-        <v>46302.000169999999</v>
+        <v>46306.000169999999</v>
       </c>
       <c r="M8">
         <f t="shared" ca="1" si="1"/>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="P8" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O8),"")</f>
-        <v>46293.000090000001</v>
+        <v>46297.000090000001</v>
       </c>
       <c r="Q8">
         <f t="shared" si="2"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="H9" s="14">
         <f ca="1">IFERROR(_xlfn.AGGREGATE(15,6,SortKey/CondFocus,$G9),"")</f>
-        <v>46303.000180000003</v>
+        <v>46307.000180000003</v>
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="0"/>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="P9" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O9),"")</f>
-        <v>46295.000099999997</v>
+        <v>46299.000099999997</v>
       </c>
       <c r="Q9">
         <f t="shared" si="2"/>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="P10" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O10),"")</f>
-        <v>46296.000110000001</v>
+        <v>46300.000110000001</v>
       </c>
       <c r="Q10">
         <f t="shared" si="2"/>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="P11" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O11),"")</f>
-        <v>46297.00013</v>
+        <v>46301.00013</v>
       </c>
       <c r="Q11">
         <f t="shared" si="2"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="P12" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O12),"")</f>
-        <v>46298.000139999996</v>
+        <v>46302.000139999996</v>
       </c>
       <c r="Q12">
         <f t="shared" si="2"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P13" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O13),"")</f>
-        <v>46299.00015</v>
+        <v>46303.00015</v>
       </c>
       <c r="Q13">
         <f t="shared" si="2"/>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="P14" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O14),"")</f>
-        <v>46300.000160000003</v>
+        <v>46304.000160000003</v>
       </c>
       <c r="Q14">
         <f t="shared" si="2"/>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="P15" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O15),"")</f>
-        <v>46302.000169999999</v>
+        <v>46306.000169999999</v>
       </c>
       <c r="Q15">
         <f t="shared" si="2"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="P16" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O16),"")</f>
-        <v>46303.000180000003</v>
+        <v>46307.000180000003</v>
       </c>
       <c r="Q16">
         <f t="shared" si="2"/>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="P17" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O17),"")</f>
-        <v>46304.000200000002</v>
+        <v>46308.000200000002</v>
       </c>
       <c r="Q17">
         <f t="shared" si="2"/>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="P18" s="14">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,SortKeyView/InScope,$O18),"")</f>
-        <v>46305.000209999998</v>
+        <v>46309.000209999998</v>
       </c>
       <c r="Q18">
         <f t="shared" si="2"/>
